--- a/KTU-consultation-analysis.xlsx
+++ b/KTU-consultation-analysis.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -632,14 +632,16 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -652,7 +654,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Tune-Up only (ServiceMinder org 1682 / location KT20191006). Bath Tune-Up is org 4761 and is not in any figure here. Service = "Consultation - In-Home"; showroom, site-visit, measuring and installation appointments excluded. Consults are grouped by the month the appointment was SCHEDULED for. 24 test/system records excluded (see column L). Proposals are real quotes only — 9 credit memos / zero-value adjustments were removed. Acceptance % is measured on DECIDED quotes so a fresh month is not punished for quotes nobody has answered yet.</t>
+          <t>Kitchen Tune-Up only (ServiceMinder org 1682 / location KT20191006). Bath Tune-Up is org 4761 and is not in any figure here. Service = "Consultation - In-Home"; showroom, site-visit, measuring and installation appointments excluded. Consults are grouped by the month the appointment was SCHEDULED for. 24 test/system records excluded (see column L). Proposals are real quotes only — 9 credit memos / zero-value adjustments were removed. Acceptance % is measured on DECIDED quotes so a fresh month is not punished for quotes nobody has answered yet. "Value quoted" is the subtotal of every real quote issued that month; "Value sold" is the subtotal of the ones that were accepted; "Win % by value" is sold divided by quoted, the value-weighted version of the acceptance rate.</t>
         </is>
       </c>
     </row>
@@ -686,7 +688,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Real quotes
+          <t>Quotes
 sent</t>
         </is>
       </c>
@@ -705,27 +707,39 @@
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Acceptance %
-(of decided)</t>
+(by count,
+of decided)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Value quoted</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>Value sold</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Win %
+by value</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Open quote
 value</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Test records
 excluded</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -764,13 +778,20 @@
         <v/>
       </c>
       <c r="J5" s="36" t="n">
+        <v>338258</v>
+      </c>
+      <c r="K5" s="36" t="n">
         <v>151393</v>
       </c>
-      <c r="K5" s="36" t="n"/>
-      <c r="L5" s="35" t="n">
+      <c r="L5" s="6">
+        <f>IF(J5=0,"",K5/J5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="36" t="n"/>
+      <c r="N5" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>Oct 2025 was the highest-volume month of the year and still cancelled 61%.</t>
         </is>
@@ -809,13 +830,20 @@
         <v/>
       </c>
       <c r="J6" s="38" t="n">
+        <v>718114</v>
+      </c>
+      <c r="K6" s="38" t="n">
         <v>229763</v>
       </c>
-      <c r="K6" s="38" t="n"/>
-      <c r="L6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="13" t="n"/>
+      <c r="L6" s="11">
+        <f>IF(J6=0,"",K6/J6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -850,13 +878,20 @@
         <v/>
       </c>
       <c r="J7" s="36" t="n">
+        <v>339220</v>
+      </c>
+      <c r="K7" s="36" t="n">
         <v>122000</v>
       </c>
-      <c r="K7" s="36" t="n"/>
-      <c r="L7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="14" t="n"/>
+      <c r="L7" s="6">
+        <f>IF(J7=0,"",K7/J7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="36" t="n"/>
+      <c r="N7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -891,13 +926,20 @@
         <v/>
       </c>
       <c r="J8" s="38" t="n">
+        <v>289427</v>
+      </c>
+      <c r="K8" s="38" t="n">
         <v>159601</v>
       </c>
-      <c r="K8" s="38" t="n"/>
-      <c r="L8" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="13" t="n"/>
+      <c r="L8" s="11">
+        <f>IF(J8=0,"",K8/J8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -932,13 +974,20 @@
         <v/>
       </c>
       <c r="J9" s="36" t="n">
+        <v>523667</v>
+      </c>
+      <c r="K9" s="36" t="n">
         <v>125628</v>
       </c>
-      <c r="K9" s="36" t="n"/>
-      <c r="L9" s="35" t="n">
+      <c r="L9" s="6">
+        <f>IF(J9=0,"",K9/J9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="36" t="n"/>
+      <c r="N9" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -973,13 +1022,20 @@
         <v/>
       </c>
       <c r="J10" s="38" t="n">
+        <v>436305</v>
+      </c>
+      <c r="K10" s="38" t="n">
         <v>251811</v>
       </c>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="13" t="n"/>
+      <c r="L10" s="11">
+        <f>IF(J10=0,"",K10/J10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1014,13 +1070,20 @@
         <v/>
       </c>
       <c r="J11" s="36" t="n">
+        <v>337601</v>
+      </c>
+      <c r="K11" s="36" t="n">
         <v>127316</v>
       </c>
-      <c r="K11" s="36" t="n"/>
-      <c r="L11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14" t="n"/>
+      <c r="L11" s="6">
+        <f>IF(J11=0,"",K11/J11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1055,13 +1118,20 @@
         <v/>
       </c>
       <c r="J12" s="38" t="n">
+        <v>298309</v>
+      </c>
+      <c r="K12" s="38" t="n">
         <v>138120</v>
       </c>
-      <c r="K12" s="38" t="n"/>
-      <c r="L12" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="13" t="n"/>
+      <c r="L12" s="11">
+        <f>IF(J12=0,"",K12/J12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1096,13 +1166,20 @@
         <v/>
       </c>
       <c r="J13" s="36" t="n">
+        <v>862065</v>
+      </c>
+      <c r="K13" s="36" t="n">
         <v>333788</v>
       </c>
-      <c r="K13" s="36" t="n"/>
-      <c r="L13" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="14" t="n"/>
+      <c r="L13" s="6">
+        <f>IF(J13=0,"",K13/J13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="36" t="n"/>
+      <c r="N13" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1137,13 +1214,20 @@
         <v/>
       </c>
       <c r="J14" s="38" t="n">
+        <v>427466</v>
+      </c>
+      <c r="K14" s="38" t="n">
         <v>101487</v>
       </c>
-      <c r="K14" s="38" t="n"/>
-      <c r="L14" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13" t="n"/>
+      <c r="L14" s="11">
+        <f>IF(J14=0,"",K14/J14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1178,15 +1262,22 @@
         <v/>
       </c>
       <c r="J15" s="36" t="n">
+        <v>930481</v>
+      </c>
+      <c r="K15" s="36" t="n">
         <v>230876</v>
       </c>
-      <c r="K15" s="36" t="n"/>
-      <c r="L15" s="35" t="n">
+      <c r="L15" s="6">
+        <f>IF(J15=0,"",K15/J15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>July: quotes written held up (35) but only 9 closed — 26%, the worst acceptance in the year.</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>July quoted $930,481 - the most of any month - and closed 25% of it. Quoting was not the problem.</t>
         </is>
       </c>
     </row>
@@ -1223,17 +1314,24 @@
         <v/>
       </c>
       <c r="J16" s="38" t="n">
+        <v>432558</v>
+      </c>
+      <c r="K16" s="38" t="n">
         <v>56970</v>
       </c>
-      <c r="K16" s="38" t="n">
+      <c r="L16" s="11">
+        <f>IF(J16=0,"",K16/J16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="38" t="n">
         <v>143784</v>
       </c>
-      <c r="L16" s="37" t="n">
+      <c r="N16" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="15" t="inlineStr">
-        <is>
-          <t>August: lowest value sold of the twelve months. 6 quotes worth $143,784 were still open at the pull date, so this figure can still rise.</t>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>August: 13 cents on the quoted dollar, less than half the next-worst month. 6 quotes worth $143,784 were still open at the pull date, so this can still rise.</t>
         </is>
       </c>
     </row>
@@ -1283,15 +1381,23 @@
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="39">
-        <f>SUM(L5:L16)</f>
-        <v/>
-      </c>
-      <c r="M17" s="20" t="n"/>
+      <c r="L17" s="18">
+        <f>K17/J17</f>
+        <v/>
+      </c>
+      <c r="M17" s="40">
+        <f>SUM(M5:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="39">
+        <f>SUM(N5:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E16">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
@@ -1308,6 +1414,14 @@
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="2">
       <formula>0.55</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L16">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>0.25</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="2">
+      <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16239,7 +16353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16404,13 +16518,25 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="84" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
+          <t>Quote values</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>"Value quoted" sums the subtotal of every real quote issued in that month; "Value sold" sums the subtotal of the ones accepted. Both are pre-tax subtotals as ServiceMinder stores them, and both are attributed to the month the quote was ISSUED, not the month it was accepted — so a quote written on 30 July and signed in August counts in July on both columns. "Win % by value" is sold divided by quoted. It runs lower than the acceptance % by count all year, which means the quotes that close are consistently the smaller ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
           <t>Percentages are live formulas</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Every % and total in this workbook is a formula over the counts beside it, not a pasted number, so the sheets stay correct if you filter or edit the underlying rows. They carry no cached result — Excel and Google Sheets compute them the moment the file opens. A lightweight preview pane that reads only cached values may show those cells blank until you open the file properly; that is the preview, not the workbook.</t>
         </is>

--- a/KTU-consultation-analysis.xlsx
+++ b/KTU-consultation-analysis.xlsx
@@ -831,9 +831,8 @@
       <c r="D5" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="6">
-        <f>IF(C5+D5=0,"",D5/(C5+D5))</f>
-        <v/>
+      <c r="E5" s="6" t="n">
+        <v>0.4</v>
       </c>
       <c r="F5" s="35" t="n">
         <v>12</v>
@@ -844,9 +843,8 @@
       <c r="H5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="6">
-        <f>IF(F5-H5=0,"",G5/(F5-H5))</f>
-        <v/>
+      <c r="I5" s="6" t="n">
+        <v>0.4166666666666667</v>
       </c>
       <c r="J5" s="36" t="n">
         <v>338258</v>
@@ -854,9 +852,8 @@
       <c r="K5" s="36" t="n">
         <v>151393</v>
       </c>
-      <c r="L5" s="6">
-        <f>IF(J5=0,"",K5/J5)</f>
-        <v/>
+      <c r="L5" s="6" t="n">
+        <v>0.4475666503083445</v>
       </c>
       <c r="M5" s="36" t="n"/>
       <c r="N5" s="35" t="n">
@@ -883,9 +880,8 @@
       <c r="D6" s="37" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="11">
-        <f>IF(C6+D6=0,"",D6/(C6+D6))</f>
-        <v/>
+      <c r="E6" s="11" t="n">
+        <v>0.6140350877192983</v>
       </c>
       <c r="F6" s="37" t="n">
         <v>38</v>
@@ -896,9 +892,8 @@
       <c r="H6" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="11">
-        <f>IF(F6-H6=0,"",G6/(F6-H6))</f>
-        <v/>
+      <c r="I6" s="11" t="n">
+        <v>0.5263157894736842</v>
       </c>
       <c r="J6" s="38" t="n">
         <v>718114</v>
@@ -906,9 +901,8 @@
       <c r="K6" s="38" t="n">
         <v>229763</v>
       </c>
-      <c r="L6" s="11">
-        <f>IF(J6=0,"",K6/J6)</f>
-        <v/>
+      <c r="L6" s="11" t="n">
+        <v>0.3199533778759361</v>
       </c>
       <c r="M6" s="38" t="n"/>
       <c r="N6" s="37" t="n">
@@ -931,9 +925,8 @@
       <c r="D7" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="6">
-        <f>IF(C7+D7=0,"",D7/(C7+D7))</f>
-        <v/>
+      <c r="E7" s="6" t="n">
+        <v>0.78125</v>
       </c>
       <c r="F7" s="35" t="n">
         <v>14</v>
@@ -944,9 +937,8 @@
       <c r="H7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="6">
-        <f>IF(F7-H7=0,"",G7/(F7-H7))</f>
-        <v/>
+      <c r="I7" s="6" t="n">
+        <v>0.5714285714285714</v>
       </c>
       <c r="J7" s="36" t="n">
         <v>339220</v>
@@ -954,9 +946,8 @@
       <c r="K7" s="36" t="n">
         <v>122000</v>
       </c>
-      <c r="L7" s="6">
-        <f>IF(J7=0,"",K7/J7)</f>
-        <v/>
+      <c r="L7" s="6" t="n">
+        <v>0.3596486056246684</v>
       </c>
       <c r="M7" s="36" t="n"/>
       <c r="N7" s="35" t="n">
@@ -979,9 +970,8 @@
       <c r="D8" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="E8" s="11">
-        <f>IF(C8+D8=0,"",D8/(C8+D8))</f>
-        <v/>
+      <c r="E8" s="11" t="n">
+        <v>0.5416666666666666</v>
       </c>
       <c r="F8" s="37" t="n">
         <v>18</v>
@@ -992,9 +982,8 @@
       <c r="H8" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="11">
-        <f>IF(F8-H8=0,"",G8/(F8-H8))</f>
-        <v/>
+      <c r="I8" s="11" t="n">
+        <v>0.6111111111111112</v>
       </c>
       <c r="J8" s="38" t="n">
         <v>289427</v>
@@ -1002,9 +991,8 @@
       <c r="K8" s="38" t="n">
         <v>159601</v>
       </c>
-      <c r="L8" s="11">
-        <f>IF(J8=0,"",K8/J8)</f>
-        <v/>
+      <c r="L8" s="11" t="n">
+        <v>0.5514378409754446</v>
       </c>
       <c r="M8" s="38" t="n"/>
       <c r="N8" s="37" t="n">
@@ -1027,9 +1015,8 @@
       <c r="D9" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="6">
-        <f>IF(C9+D9=0,"",D9/(C9+D9))</f>
-        <v/>
+      <c r="E9" s="6" t="n">
+        <v>0.4411764705882353</v>
       </c>
       <c r="F9" s="35" t="n">
         <v>33</v>
@@ -1040,9 +1027,8 @@
       <c r="H9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6">
-        <f>IF(F9-H9=0,"",G9/(F9-H9))</f>
-        <v/>
+      <c r="I9" s="6" t="n">
+        <v>0.4242424242424243</v>
       </c>
       <c r="J9" s="36" t="n">
         <v>523667</v>
@@ -1050,9 +1036,8 @@
       <c r="K9" s="36" t="n">
         <v>125628</v>
       </c>
-      <c r="L9" s="6">
-        <f>IF(J9=0,"",K9/J9)</f>
-        <v/>
+      <c r="L9" s="6" t="n">
+        <v>0.2399005474853294</v>
       </c>
       <c r="M9" s="36" t="n"/>
       <c r="N9" s="35" t="n">
@@ -1075,9 +1060,8 @@
       <c r="D10" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="11">
-        <f>IF(C10+D10=0,"",D10/(C10+D10))</f>
-        <v/>
+      <c r="E10" s="11" t="n">
+        <v>0.4193548387096774</v>
       </c>
       <c r="F10" s="37" t="n">
         <v>22</v>
@@ -1088,9 +1072,8 @@
       <c r="H10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="11">
-        <f>IF(F10-H10=0,"",G10/(F10-H10))</f>
-        <v/>
+      <c r="I10" s="11" t="n">
+        <v>0.6363636363636364</v>
       </c>
       <c r="J10" s="38" t="n">
         <v>436305</v>
@@ -1098,9 +1081,8 @@
       <c r="K10" s="38" t="n">
         <v>251811</v>
       </c>
-      <c r="L10" s="11">
-        <f>IF(J10=0,"",K10/J10)</f>
-        <v/>
+      <c r="L10" s="11" t="n">
+        <v>0.5771444287826176</v>
       </c>
       <c r="M10" s="38" t="n"/>
       <c r="N10" s="37" t="n">
@@ -1123,9 +1105,8 @@
       <c r="D11" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="E11" s="6">
-        <f>IF(C11+D11=0,"",D11/(C11+D11))</f>
-        <v/>
+      <c r="E11" s="6" t="n">
+        <v>0.5757575757575758</v>
       </c>
       <c r="F11" s="35" t="n">
         <v>15</v>
@@ -1136,9 +1117,8 @@
       <c r="H11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="6">
-        <f>IF(F11-H11=0,"",G11/(F11-H11))</f>
-        <v/>
+      <c r="I11" s="6" t="n">
+        <v>0.5333333333333333</v>
       </c>
       <c r="J11" s="36" t="n">
         <v>337601</v>
@@ -1146,9 +1126,8 @@
       <c r="K11" s="36" t="n">
         <v>127316</v>
       </c>
-      <c r="L11" s="6">
-        <f>IF(J11=0,"",K11/J11)</f>
-        <v/>
+      <c r="L11" s="6" t="n">
+        <v>0.3771197360197393</v>
       </c>
       <c r="M11" s="36" t="n"/>
       <c r="N11" s="35" t="n">
@@ -1171,9 +1150,8 @@
       <c r="D12" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="E12" s="11">
-        <f>IF(C12+D12=0,"",D12/(C12+D12))</f>
-        <v/>
+      <c r="E12" s="11" t="n">
+        <v>0.7</v>
       </c>
       <c r="F12" s="37" t="n">
         <v>14</v>
@@ -1184,9 +1162,8 @@
       <c r="H12" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="11">
-        <f>IF(F12-H12=0,"",G12/(F12-H12))</f>
-        <v/>
+      <c r="I12" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="J12" s="38" t="n">
         <v>298309</v>
@@ -1194,9 +1171,8 @@
       <c r="K12" s="38" t="n">
         <v>138120</v>
       </c>
-      <c r="L12" s="11">
-        <f>IF(J12=0,"",K12/J12)</f>
-        <v/>
+      <c r="L12" s="11" t="n">
+        <v>0.463009832086863</v>
       </c>
       <c r="M12" s="38" t="n"/>
       <c r="N12" s="37" t="n">
@@ -1219,9 +1195,8 @@
       <c r="D13" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="E13" s="6">
-        <f>IF(C13+D13=0,"",D13/(C13+D13))</f>
-        <v/>
+      <c r="E13" s="6" t="n">
+        <v>0.4081632653061225</v>
       </c>
       <c r="F13" s="35" t="n">
         <v>38</v>
@@ -1232,9 +1207,8 @@
       <c r="H13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6">
-        <f>IF(F13-H13=0,"",G13/(F13-H13))</f>
-        <v/>
+      <c r="I13" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="J13" s="36" t="n">
         <v>862065</v>
@@ -1242,9 +1216,8 @@
       <c r="K13" s="36" t="n">
         <v>333788</v>
       </c>
-      <c r="L13" s="6">
-        <f>IF(J13=0,"",K13/J13)</f>
-        <v/>
+      <c r="L13" s="6" t="n">
+        <v>0.387195861100961</v>
       </c>
       <c r="M13" s="36" t="n"/>
       <c r="N13" s="35" t="n">
@@ -1267,9 +1240,8 @@
       <c r="D14" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="E14" s="11">
-        <f>IF(C14+D14=0,"",D14/(C14+D14))</f>
-        <v/>
+      <c r="E14" s="11" t="n">
+        <v>0.5384615384615384</v>
       </c>
       <c r="F14" s="37" t="n">
         <v>18</v>
@@ -1280,9 +1252,8 @@
       <c r="H14" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="11">
-        <f>IF(F14-H14=0,"",G14/(F14-H14))</f>
-        <v/>
+      <c r="I14" s="11" t="n">
+        <v>0.4444444444444444</v>
       </c>
       <c r="J14" s="38" t="n">
         <v>427466</v>
@@ -1290,9 +1261,8 @@
       <c r="K14" s="38" t="n">
         <v>101487</v>
       </c>
-      <c r="L14" s="11">
-        <f>IF(J14=0,"",K14/J14)</f>
-        <v/>
+      <c r="L14" s="11" t="n">
+        <v>0.2374153733864214</v>
       </c>
       <c r="M14" s="38" t="n"/>
       <c r="N14" s="37" t="n">
@@ -1315,9 +1285,8 @@
       <c r="D15" s="35" t="n">
         <v>31</v>
       </c>
-      <c r="E15" s="6">
-        <f>IF(C15+D15=0,"",D15/(C15+D15))</f>
-        <v/>
+      <c r="E15" s="6" t="n">
+        <v>0.6458333333333334</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>35</v>
@@ -1328,9 +1297,8 @@
       <c r="H15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="6">
-        <f>IF(F15-H15=0,"",G15/(F15-H15))</f>
-        <v/>
+      <c r="I15" s="6" t="n">
+        <v>0.2571428571428571</v>
       </c>
       <c r="J15" s="36" t="n">
         <v>930481</v>
@@ -1338,9 +1306,8 @@
       <c r="K15" s="36" t="n">
         <v>230876</v>
       </c>
-      <c r="L15" s="6">
-        <f>IF(J15=0,"",K15/J15)</f>
-        <v/>
+      <c r="L15" s="6" t="n">
+        <v>0.2481254319002752</v>
       </c>
       <c r="M15" s="36" t="n"/>
       <c r="N15" s="35" t="n">
@@ -1367,9 +1334,8 @@
       <c r="D16" s="37" t="n">
         <v>32</v>
       </c>
-      <c r="E16" s="11">
-        <f>IF(C16+D16=0,"",D16/(C16+D16))</f>
-        <v/>
+      <c r="E16" s="11" t="n">
+        <v>0.7272727272727273</v>
       </c>
       <c r="F16" s="37" t="n">
         <v>18</v>
@@ -1380,9 +1346,8 @@
       <c r="H16" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="11">
-        <f>IF(F16-H16=0,"",G16/(F16-H16))</f>
-        <v/>
+      <c r="I16" s="11" t="n">
+        <v>0.4166666666666667</v>
       </c>
       <c r="J16" s="38" t="n">
         <v>432558</v>
@@ -1390,9 +1355,8 @@
       <c r="K16" s="38" t="n">
         <v>56970</v>
       </c>
-      <c r="L16" s="11">
-        <f>IF(J16=0,"",K16/J16)</f>
-        <v/>
+      <c r="L16" s="11" t="n">
+        <v>0.131704881195123</v>
       </c>
       <c r="M16" s="38" t="n">
         <v>143784</v>
@@ -1412,57 +1376,44 @@
           <t>12-month total</t>
         </is>
       </c>
-      <c r="B17" s="39">
-        <f>SUM(B5:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="39">
-        <f>SUM(C5:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="18">
-        <f>D17/(C17+D17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
-        <f>SUM(F5:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>SUM(G5:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>SUM(H5:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="18">
-        <f>G17/(F17-H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="40">
-        <f>SUM(J5:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="40">
-        <f>SUM(K5:K16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="18">
-        <f>K17/J17</f>
-        <v/>
-      </c>
-      <c r="M17" s="40">
-        <f>SUM(M5:M16)</f>
-        <v/>
-      </c>
-      <c r="N17" s="39">
-        <f>SUM(N5:N16)</f>
-        <v/>
+      <c r="B17" s="39" t="n">
+        <v>437</v>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>185</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>251</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0.5756880733944955</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>275</v>
+      </c>
+      <c r="G17" s="39" t="n">
+        <v>128</v>
+      </c>
+      <c r="H17" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>0.4758364312267658</v>
+      </c>
+      <c r="J17" s="40" t="n">
+        <v>5933471</v>
+      </c>
+      <c r="K17" s="40" t="n">
+        <v>2028753</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <v>0.3419167296848674</v>
+      </c>
+      <c r="M17" s="40" t="n">
+        <v>143784</v>
+      </c>
+      <c r="N17" s="39" t="n">
+        <v>24</v>
       </c>
       <c r="O17" s="20" t="n"/>
     </row>
@@ -1588,9 +1539,8 @@
       <c r="E5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="6">
-        <f>IF(D5+E5=0,"",E5/(D5+E5))</f>
-        <v/>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="14" t="inlineStr"/>
     </row>
@@ -1614,9 +1564,8 @@
       <c r="E6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="11">
-        <f>IF(D6+E6=0,"",E6/(D6+E6))</f>
-        <v/>
+      <c r="F6" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G6" s="13" t="inlineStr"/>
     </row>
@@ -1640,9 +1589,8 @@
       <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="6">
-        <f>IF(D7+E7=0,"",E7/(D7+E7))</f>
-        <v/>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G7" s="14" t="inlineStr"/>
     </row>
@@ -1666,9 +1614,8 @@
       <c r="E8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="11">
-        <f>IF(D8+E8=0,"",E8/(D8+E8))</f>
-        <v/>
+      <c r="F8" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
     </row>
@@ -1692,9 +1639,8 @@
       <c r="E9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="6">
-        <f>IF(D9+E9=0,"",E9/(D9+E9))</f>
-        <v/>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="14" t="inlineStr"/>
     </row>
@@ -1718,9 +1664,8 @@
       <c r="E10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="11">
-        <f>IF(D10+E10=0,"",E10/(D10+E10))</f>
-        <v/>
+      <c r="F10" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G10" s="13" t="inlineStr"/>
     </row>
@@ -1744,9 +1689,8 @@
       <c r="E11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="6">
-        <f>IF(D11+E11=0,"",E11/(D11+E11))</f>
-        <v/>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="14" t="inlineStr"/>
     </row>
@@ -1770,9 +1714,8 @@
       <c r="E12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11">
-        <f>IF(D12+E12=0,"",E12/(D12+E12))</f>
-        <v/>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="13" t="inlineStr"/>
     </row>
@@ -1796,9 +1739,8 @@
       <c r="E13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="6">
-        <f>IF(D13+E13=0,"",E13/(D13+E13))</f>
-        <v/>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="14" t="inlineStr"/>
     </row>
@@ -1822,9 +1764,8 @@
       <c r="E14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="11">
-        <f>IF(D14+E14=0,"",E14/(D14+E14))</f>
-        <v/>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="13" t="inlineStr"/>
     </row>
@@ -1848,9 +1789,8 @@
       <c r="E15" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="6">
-        <f>IF(D15+E15=0,"",E15/(D15+E15))</f>
-        <v/>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
     </row>
@@ -1874,9 +1814,8 @@
       <c r="E16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="11">
-        <f>IF(D16+E16=0,"",E16/(D16+E16))</f>
-        <v/>
+      <c r="F16" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="13" t="inlineStr"/>
     </row>
@@ -1900,9 +1839,8 @@
       <c r="E17" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="6">
-        <f>IF(D17+E17=0,"",E17/(D17+E17))</f>
-        <v/>
+      <c r="F17" s="6" t="n">
+        <v>0.7777777777777778</v>
       </c>
       <c r="G17" s="14" t="inlineStr"/>
     </row>
@@ -1926,9 +1864,8 @@
       <c r="E18" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="11">
-        <f>IF(D18+E18=0,"",E18/(D18+E18))</f>
-        <v/>
+      <c r="F18" s="11" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="G18" s="13" t="inlineStr"/>
     </row>
@@ -1952,9 +1889,8 @@
       <c r="E19" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="6">
-        <f>IF(D19+E19=0,"",E19/(D19+E19))</f>
-        <v/>
+      <c r="F19" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G19" s="14" t="inlineStr"/>
     </row>
@@ -1978,9 +1914,8 @@
       <c r="E20" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="11">
-        <f>IF(D20+E20=0,"",E20/(D20+E20))</f>
-        <v/>
+      <c r="F20" s="11" t="n">
+        <v>0.4285714285714285</v>
       </c>
       <c r="G20" s="13" t="inlineStr"/>
     </row>
@@ -2004,9 +1939,8 @@
       <c r="E21" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="6">
-        <f>IF(D21+E21=0,"",E21/(D21+E21))</f>
-        <v/>
+      <c r="F21" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="14" t="inlineStr"/>
     </row>
@@ -2030,9 +1964,8 @@
       <c r="E22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="11">
-        <f>IF(D22+E22=0,"",E22/(D22+E22))</f>
-        <v/>
+      <c r="F22" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="inlineStr"/>
     </row>
@@ -2056,9 +1989,8 @@
       <c r="E23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="6">
-        <f>IF(D23+E23=0,"",E23/(D23+E23))</f>
-        <v/>
+      <c r="F23" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G23" s="14" t="inlineStr"/>
     </row>
@@ -2082,9 +2014,8 @@
       <c r="E24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11">
-        <f>IF(D24+E24=0,"",E24/(D24+E24))</f>
-        <v/>
+      <c r="F24" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G24" s="13" t="inlineStr"/>
     </row>
@@ -2108,9 +2039,8 @@
       <c r="E25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="6">
-        <f>IF(D25+E25=0,"",E25/(D25+E25))</f>
-        <v/>
+      <c r="F25" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G25" s="14" t="inlineStr"/>
     </row>
@@ -2134,9 +2064,8 @@
       <c r="E26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="11">
-        <f>IF(D26+E26=0,"",E26/(D26+E26))</f>
-        <v/>
+      <c r="F26" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="13" t="inlineStr"/>
     </row>
@@ -2160,9 +2089,8 @@
       <c r="E27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="6">
-        <f>IF(D27+E27=0,"",E27/(D27+E27))</f>
-        <v/>
+      <c r="F27" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="14" t="inlineStr"/>
     </row>
@@ -2186,9 +2114,8 @@
       <c r="E28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="11">
-        <f>IF(D28+E28=0,"",E28/(D28+E28))</f>
-        <v/>
+      <c r="F28" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
     </row>
@@ -2212,9 +2139,8 @@
       <c r="E29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="6">
-        <f>IF(D29+E29=0,"",E29/(D29+E29))</f>
-        <v/>
+      <c r="F29" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G29" s="14" t="inlineStr"/>
     </row>
@@ -2238,9 +2164,8 @@
       <c r="E30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11">
-        <f>IF(D30+E30=0,"",E30/(D30+E30))</f>
-        <v/>
+      <c r="F30" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
     </row>
@@ -2264,9 +2189,8 @@
       <c r="E31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="6">
-        <f>IF(D31+E31=0,"",E31/(D31+E31))</f>
-        <v/>
+      <c r="F31" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G31" s="14" t="inlineStr"/>
     </row>
@@ -2290,9 +2214,8 @@
       <c r="E32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="11">
-        <f>IF(D32+E32=0,"",E32/(D32+E32))</f>
-        <v/>
+      <c r="F32" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
     </row>
@@ -2316,9 +2239,8 @@
       <c r="E33" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="6">
-        <f>IF(D33+E33=0,"",E33/(D33+E33))</f>
-        <v/>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G33" s="14" t="inlineStr"/>
     </row>
@@ -2342,9 +2264,8 @@
       <c r="E34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="11">
-        <f>IF(D34+E34=0,"",E34/(D34+E34))</f>
-        <v/>
+      <c r="F34" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G34" s="13" t="inlineStr"/>
     </row>
@@ -2368,9 +2289,8 @@
       <c r="E35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="6">
-        <f>IF(D35+E35=0,"",E35/(D35+E35))</f>
-        <v/>
+      <c r="F35" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G35" s="14" t="inlineStr"/>
     </row>
@@ -2394,9 +2314,8 @@
       <c r="E36" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="11">
-        <f>IF(D36+E36=0,"",E36/(D36+E36))</f>
-        <v/>
+      <c r="F36" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="13" t="inlineStr"/>
     </row>
@@ -2420,9 +2339,8 @@
       <c r="E37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="6">
-        <f>IF(D37+E37=0,"",E37/(D37+E37))</f>
-        <v/>
+      <c r="F37" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G37" s="14" t="inlineStr"/>
     </row>
@@ -2446,9 +2364,8 @@
       <c r="E38" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="11">
-        <f>IF(D38+E38=0,"",E38/(D38+E38))</f>
-        <v/>
+      <c r="F38" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
     </row>
@@ -2472,9 +2389,8 @@
       <c r="E39" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="6">
-        <f>IF(D39+E39=0,"",E39/(D39+E39))</f>
-        <v/>
+      <c r="F39" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G39" s="14" t="inlineStr"/>
     </row>
@@ -2498,10 +2414,7 @@
       <c r="E40" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="11">
-        <f>IF(D40+E40=0,"",E40/(D40+E40))</f>
-        <v/>
-      </c>
+      <c r="F40" s="11" t="n"/>
       <c r="G40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2524,9 +2437,8 @@
       <c r="E41" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="6">
-        <f>IF(D41+E41=0,"",E41/(D41+E41))</f>
-        <v/>
+      <c r="F41" s="6" t="n">
+        <v>0.625</v>
       </c>
       <c r="G41" s="14" t="inlineStr"/>
     </row>
@@ -2550,9 +2462,8 @@
       <c r="E42" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F42" s="11">
-        <f>IF(D42+E42=0,"",E42/(D42+E42))</f>
-        <v/>
+      <c r="F42" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G42" s="13" t="inlineStr"/>
     </row>
@@ -2576,9 +2487,8 @@
       <c r="E43" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6">
-        <f>IF(D43+E43=0,"",E43/(D43+E43))</f>
-        <v/>
+      <c r="F43" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G43" s="14" t="inlineStr"/>
     </row>
@@ -2602,9 +2512,8 @@
       <c r="E44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="11">
-        <f>IF(D44+E44=0,"",E44/(D44+E44))</f>
-        <v/>
+      <c r="F44" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
     </row>
@@ -2628,9 +2537,8 @@
       <c r="E45" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="6">
-        <f>IF(D45+E45=0,"",E45/(D45+E45))</f>
-        <v/>
+      <c r="F45" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G45" s="14" t="inlineStr"/>
     </row>
@@ -2654,9 +2562,8 @@
       <c r="E46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="11">
-        <f>IF(D46+E46=0,"",E46/(D46+E46))</f>
-        <v/>
+      <c r="F46" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G46" s="13" t="inlineStr"/>
     </row>
@@ -2680,9 +2587,8 @@
       <c r="E47" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="6">
-        <f>IF(D47+E47=0,"",E47/(D47+E47))</f>
-        <v/>
+      <c r="F47" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G47" s="14" t="inlineStr"/>
     </row>
@@ -2706,9 +2612,8 @@
       <c r="E48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="11">
-        <f>IF(D48+E48=0,"",E48/(D48+E48))</f>
-        <v/>
+      <c r="F48" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G48" s="13" t="inlineStr"/>
     </row>
@@ -2732,9 +2637,8 @@
       <c r="E49" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="6">
-        <f>IF(D49+E49=0,"",E49/(D49+E49))</f>
-        <v/>
+      <c r="F49" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G49" s="14" t="inlineStr"/>
     </row>
@@ -2758,9 +2662,8 @@
       <c r="E50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="11">
-        <f>IF(D50+E50=0,"",E50/(D50+E50))</f>
-        <v/>
+      <c r="F50" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
     </row>
@@ -2784,9 +2687,8 @@
       <c r="E51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="6">
-        <f>IF(D51+E51=0,"",E51/(D51+E51))</f>
-        <v/>
+      <c r="F51" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G51" s="14" t="inlineStr"/>
     </row>
@@ -2810,9 +2712,8 @@
       <c r="E52" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="11">
-        <f>IF(D52+E52=0,"",E52/(D52+E52))</f>
-        <v/>
+      <c r="F52" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G52" s="13" t="inlineStr"/>
     </row>
@@ -2836,9 +2737,8 @@
       <c r="E53" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="6">
-        <f>IF(D53+E53=0,"",E53/(D53+E53))</f>
-        <v/>
+      <c r="F53" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G53" s="14" t="inlineStr"/>
     </row>
@@ -2862,9 +2762,8 @@
       <c r="E54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="11">
-        <f>IF(D54+E54=0,"",E54/(D54+E54))</f>
-        <v/>
+      <c r="F54" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G54" s="13" t="inlineStr"/>
     </row>
@@ -2888,9 +2787,8 @@
       <c r="E55" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="6">
-        <f>IF(D55+E55=0,"",E55/(D55+E55))</f>
-        <v/>
+      <c r="F55" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G55" s="14" t="inlineStr"/>
     </row>
@@ -2914,9 +2812,8 @@
       <c r="E56" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="11">
-        <f>IF(D56+E56=0,"",E56/(D56+E56))</f>
-        <v/>
+      <c r="F56" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G56" s="13" t="inlineStr"/>
     </row>
@@ -2940,9 +2837,8 @@
       <c r="E57" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F57" s="6">
-        <f>IF(D57+E57=0,"",E57/(D57+E57))</f>
-        <v/>
+      <c r="F57" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="G57" s="14" t="inlineStr"/>
     </row>
@@ -2966,9 +2862,8 @@
       <c r="E58" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="11">
-        <f>IF(D58+E58=0,"",E58/(D58+E58))</f>
-        <v/>
+      <c r="F58" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G58" s="13" t="inlineStr"/>
     </row>
@@ -2992,9 +2887,8 @@
       <c r="E59" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="6">
-        <f>IF(D59+E59=0,"",E59/(D59+E59))</f>
-        <v/>
+      <c r="F59" s="6" t="n">
+        <v>0.4</v>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
     </row>
@@ -3018,9 +2912,8 @@
       <c r="E60" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11">
-        <f>IF(D60+E60=0,"",E60/(D60+E60))</f>
-        <v/>
+      <c r="F60" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G60" s="13" t="inlineStr"/>
     </row>
@@ -3044,9 +2937,8 @@
       <c r="E61" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="6">
-        <f>IF(D61+E61=0,"",E61/(D61+E61))</f>
-        <v/>
+      <c r="F61" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G61" s="14" t="inlineStr"/>
     </row>
@@ -3070,9 +2962,8 @@
       <c r="E62" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="11">
-        <f>IF(D62+E62=0,"",E62/(D62+E62))</f>
-        <v/>
+      <c r="F62" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G62" s="13" t="inlineStr"/>
     </row>
@@ -3096,9 +2987,8 @@
       <c r="E63" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="6">
-        <f>IF(D63+E63=0,"",E63/(D63+E63))</f>
-        <v/>
+      <c r="F63" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G63" s="14" t="inlineStr"/>
     </row>
@@ -3122,9 +3012,8 @@
       <c r="E64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="11">
-        <f>IF(D64+E64=0,"",E64/(D64+E64))</f>
-        <v/>
+      <c r="F64" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G64" s="13" t="inlineStr"/>
     </row>
@@ -3148,9 +3037,8 @@
       <c r="E65" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="6">
-        <f>IF(D65+E65=0,"",E65/(D65+E65))</f>
-        <v/>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G65" s="14" t="inlineStr"/>
     </row>
@@ -3174,9 +3062,8 @@
       <c r="E66" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="11">
-        <f>IF(D66+E66=0,"",E66/(D66+E66))</f>
-        <v/>
+      <c r="F66" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G66" s="13" t="inlineStr"/>
     </row>
@@ -3200,9 +3087,8 @@
       <c r="E67" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="6">
-        <f>IF(D67+E67=0,"",E67/(D67+E67))</f>
-        <v/>
+      <c r="F67" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G67" s="14" t="inlineStr"/>
     </row>
@@ -3226,9 +3112,8 @@
       <c r="E68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="11">
-        <f>IF(D68+E68=0,"",E68/(D68+E68))</f>
-        <v/>
+      <c r="F68" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3256,9 +3141,8 @@
       <c r="E69" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="6">
-        <f>IF(D69+E69=0,"",E69/(D69+E69))</f>
-        <v/>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G69" s="14" t="inlineStr"/>
     </row>
@@ -3282,9 +3166,8 @@
       <c r="E70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="11">
-        <f>IF(D70+E70=0,"",E70/(D70+E70))</f>
-        <v/>
+      <c r="F70" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G70" s="13" t="inlineStr"/>
     </row>
@@ -3308,9 +3191,8 @@
       <c r="E71" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="6">
-        <f>IF(D71+E71=0,"",E71/(D71+E71))</f>
-        <v/>
+      <c r="F71" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G71" s="14" t="inlineStr"/>
     </row>
@@ -3334,9 +3216,8 @@
       <c r="E72" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="11">
-        <f>IF(D72+E72=0,"",E72/(D72+E72))</f>
-        <v/>
+      <c r="F72" s="11" t="n">
+        <v>0.8</v>
       </c>
       <c r="G72" s="13" t="inlineStr"/>
     </row>
@@ -3360,9 +3241,8 @@
       <c r="E73" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="6">
-        <f>IF(D73+E73=0,"",E73/(D73+E73))</f>
-        <v/>
+      <c r="F73" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G73" s="14" t="inlineStr"/>
     </row>
@@ -3386,9 +3266,8 @@
       <c r="E74" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="11">
-        <f>IF(D74+E74=0,"",E74/(D74+E74))</f>
-        <v/>
+      <c r="F74" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G74" s="13" t="inlineStr"/>
     </row>
@@ -3412,9 +3291,8 @@
       <c r="E75" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F75" s="6">
-        <f>IF(D75+E75=0,"",E75/(D75+E75))</f>
-        <v/>
+      <c r="F75" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G75" s="14" t="inlineStr"/>
     </row>
@@ -3438,9 +3316,8 @@
       <c r="E76" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="11">
-        <f>IF(D76+E76=0,"",E76/(D76+E76))</f>
-        <v/>
+      <c r="F76" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G76" s="13" t="inlineStr"/>
     </row>
@@ -3464,9 +3341,8 @@
       <c r="E77" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="6">
-        <f>IF(D77+E77=0,"",E77/(D77+E77))</f>
-        <v/>
+      <c r="F77" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
     </row>
@@ -3490,9 +3366,8 @@
       <c r="E78" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="11">
-        <f>IF(D78+E78=0,"",E78/(D78+E78))</f>
-        <v/>
+      <c r="F78" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G78" s="13" t="inlineStr"/>
     </row>
@@ -3516,9 +3391,8 @@
       <c r="E79" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="6">
-        <f>IF(D79+E79=0,"",E79/(D79+E79))</f>
-        <v/>
+      <c r="F79" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
     </row>
@@ -3542,9 +3416,8 @@
       <c r="E80" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="11">
-        <f>IF(D80+E80=0,"",E80/(D80+E80))</f>
-        <v/>
+      <c r="F80" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G80" s="13" t="inlineStr"/>
     </row>
@@ -3568,9 +3441,8 @@
       <c r="E81" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="6">
-        <f>IF(D81+E81=0,"",E81/(D81+E81))</f>
-        <v/>
+      <c r="F81" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G81" s="14" t="inlineStr"/>
     </row>
@@ -3594,9 +3466,8 @@
       <c r="E82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="11">
-        <f>IF(D82+E82=0,"",E82/(D82+E82))</f>
-        <v/>
+      <c r="F82" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G82" s="13" t="inlineStr"/>
     </row>
@@ -3620,9 +3491,8 @@
       <c r="E83" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="6">
-        <f>IF(D83+E83=0,"",E83/(D83+E83))</f>
-        <v/>
+      <c r="F83" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G83" s="14" t="inlineStr"/>
     </row>
@@ -3646,9 +3516,8 @@
       <c r="E84" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="11">
-        <f>IF(D84+E84=0,"",E84/(D84+E84))</f>
-        <v/>
+      <c r="F84" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="13" t="inlineStr"/>
     </row>
@@ -3672,9 +3541,8 @@
       <c r="E85" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="6">
-        <f>IF(D85+E85=0,"",E85/(D85+E85))</f>
-        <v/>
+      <c r="F85" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G85" s="14" t="inlineStr"/>
     </row>
@@ -3698,9 +3566,8 @@
       <c r="E86" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="11">
-        <f>IF(D86+E86=0,"",E86/(D86+E86))</f>
-        <v/>
+      <c r="F86" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G86" s="13" t="inlineStr"/>
     </row>
@@ -3724,9 +3591,8 @@
       <c r="E87" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="6">
-        <f>IF(D87+E87=0,"",E87/(D87+E87))</f>
-        <v/>
+      <c r="F87" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G87" s="14" t="inlineStr"/>
     </row>
@@ -3750,9 +3616,8 @@
       <c r="E88" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="11">
-        <f>IF(D88+E88=0,"",E88/(D88+E88))</f>
-        <v/>
+      <c r="F88" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G88" s="13" t="inlineStr"/>
     </row>
@@ -3776,9 +3641,8 @@
       <c r="E89" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="6">
-        <f>IF(D89+E89=0,"",E89/(D89+E89))</f>
-        <v/>
+      <c r="F89" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G89" s="14" t="inlineStr"/>
     </row>
@@ -3802,9 +3666,8 @@
       <c r="E90" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="11">
-        <f>IF(D90+E90=0,"",E90/(D90+E90))</f>
-        <v/>
+      <c r="F90" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G90" s="13" t="inlineStr"/>
     </row>
@@ -3828,9 +3691,8 @@
       <c r="E91" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="6">
-        <f>IF(D91+E91=0,"",E91/(D91+E91))</f>
-        <v/>
+      <c r="F91" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G91" s="14" t="inlineStr"/>
     </row>
@@ -3854,9 +3716,8 @@
       <c r="E92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="11">
-        <f>IF(D92+E92=0,"",E92/(D92+E92))</f>
-        <v/>
+      <c r="F92" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G92" s="13" t="inlineStr"/>
     </row>
@@ -3880,9 +3741,8 @@
       <c r="E93" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="6">
-        <f>IF(D93+E93=0,"",E93/(D93+E93))</f>
-        <v/>
+      <c r="F93" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G93" s="14" t="inlineStr"/>
     </row>
@@ -3906,9 +3766,8 @@
       <c r="E94" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="11">
-        <f>IF(D94+E94=0,"",E94/(D94+E94))</f>
-        <v/>
+      <c r="F94" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G94" s="13" t="inlineStr"/>
     </row>
@@ -3932,9 +3791,8 @@
       <c r="E95" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="6">
-        <f>IF(D95+E95=0,"",E95/(D95+E95))</f>
-        <v/>
+      <c r="F95" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="14" t="inlineStr"/>
     </row>
@@ -3958,9 +3816,8 @@
       <c r="E96" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="11">
-        <f>IF(D96+E96=0,"",E96/(D96+E96))</f>
-        <v/>
+      <c r="F96" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G96" s="13" t="inlineStr"/>
     </row>
@@ -3984,9 +3841,8 @@
       <c r="E97" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="6">
-        <f>IF(D97+E97=0,"",E97/(D97+E97))</f>
-        <v/>
+      <c r="F97" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G97" s="14" t="inlineStr"/>
     </row>
@@ -4010,9 +3866,8 @@
       <c r="E98" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F98" s="11">
-        <f>IF(D98+E98=0,"",E98/(D98+E98))</f>
-        <v/>
+      <c r="F98" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G98" s="13" t="inlineStr"/>
     </row>
@@ -4036,9 +3891,8 @@
       <c r="E99" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="6">
-        <f>IF(D99+E99=0,"",E99/(D99+E99))</f>
-        <v/>
+      <c r="F99" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G99" s="14" t="inlineStr"/>
     </row>
@@ -4062,9 +3916,8 @@
       <c r="E100" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="11">
-        <f>IF(D100+E100=0,"",E100/(D100+E100))</f>
-        <v/>
+      <c r="F100" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="13" t="inlineStr"/>
     </row>
@@ -4088,9 +3941,8 @@
       <c r="E101" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="6">
-        <f>IF(D101+E101=0,"",E101/(D101+E101))</f>
-        <v/>
+      <c r="F101" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="14" t="inlineStr"/>
     </row>
@@ -4114,9 +3966,8 @@
       <c r="E102" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="11">
-        <f>IF(D102+E102=0,"",E102/(D102+E102))</f>
-        <v/>
+      <c r="F102" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="13" t="inlineStr"/>
     </row>
@@ -4140,9 +3991,8 @@
       <c r="E103" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F103" s="6">
-        <f>IF(D103+E103=0,"",E103/(D103+E103))</f>
-        <v/>
+      <c r="F103" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G103" s="14" t="inlineStr"/>
     </row>
@@ -4166,9 +4016,8 @@
       <c r="E104" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="11">
-        <f>IF(D104+E104=0,"",E104/(D104+E104))</f>
-        <v/>
+      <c r="F104" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G104" s="13" t="inlineStr"/>
     </row>
@@ -4192,9 +4041,8 @@
       <c r="E105" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="6">
-        <f>IF(D105+E105=0,"",E105/(D105+E105))</f>
-        <v/>
+      <c r="F105" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="14" t="inlineStr"/>
     </row>
@@ -4218,9 +4066,8 @@
       <c r="E106" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F106" s="11">
-        <f>IF(D106+E106=0,"",E106/(D106+E106))</f>
-        <v/>
+      <c r="F106" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G106" s="13" t="inlineStr"/>
     </row>
@@ -4244,9 +4091,8 @@
       <c r="E107" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="6">
-        <f>IF(D107+E107=0,"",E107/(D107+E107))</f>
-        <v/>
+      <c r="F107" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G107" s="14" t="inlineStr"/>
     </row>
@@ -4270,9 +4116,8 @@
       <c r="E108" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="11">
-        <f>IF(D108+E108=0,"",E108/(D108+E108))</f>
-        <v/>
+      <c r="F108" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G108" s="13" t="inlineStr"/>
     </row>
@@ -4296,9 +4141,8 @@
       <c r="E109" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F109" s="6">
-        <f>IF(D109+E109=0,"",E109/(D109+E109))</f>
-        <v/>
+      <c r="F109" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G109" s="14" t="inlineStr"/>
     </row>
@@ -4322,9 +4166,8 @@
       <c r="E110" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F110" s="11">
-        <f>IF(D110+E110=0,"",E110/(D110+E110))</f>
-        <v/>
+      <c r="F110" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G110" s="13" t="inlineStr"/>
     </row>
@@ -4348,9 +4191,8 @@
       <c r="E111" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="6">
-        <f>IF(D111+E111=0,"",E111/(D111+E111))</f>
-        <v/>
+      <c r="F111" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G111" s="14" t="inlineStr"/>
     </row>
@@ -4374,9 +4216,8 @@
       <c r="E112" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F112" s="11">
-        <f>IF(D112+E112=0,"",E112/(D112+E112))</f>
-        <v/>
+      <c r="F112" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G112" s="13" t="inlineStr"/>
     </row>
@@ -4400,9 +4241,8 @@
       <c r="E113" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="6">
-        <f>IF(D113+E113=0,"",E113/(D113+E113))</f>
-        <v/>
+      <c r="F113" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G113" s="14" t="inlineStr"/>
     </row>
@@ -4426,9 +4266,8 @@
       <c r="E114" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="11">
-        <f>IF(D114+E114=0,"",E114/(D114+E114))</f>
-        <v/>
+      <c r="F114" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G114" s="13" t="inlineStr"/>
     </row>
@@ -4452,9 +4291,8 @@
       <c r="E115" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F115" s="6">
-        <f>IF(D115+E115=0,"",E115/(D115+E115))</f>
-        <v/>
+      <c r="F115" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G115" s="14" t="inlineStr"/>
     </row>
@@ -4478,9 +4316,8 @@
       <c r="E116" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="11">
-        <f>IF(D116+E116=0,"",E116/(D116+E116))</f>
-        <v/>
+      <c r="F116" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G116" s="13" t="inlineStr"/>
     </row>
@@ -4504,9 +4341,8 @@
       <c r="E117" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F117" s="6">
-        <f>IF(D117+E117=0,"",E117/(D117+E117))</f>
-        <v/>
+      <c r="F117" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G117" s="14" t="inlineStr"/>
     </row>
@@ -4530,9 +4366,8 @@
       <c r="E118" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="11">
-        <f>IF(D118+E118=0,"",E118/(D118+E118))</f>
-        <v/>
+      <c r="F118" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G118" s="13" t="inlineStr"/>
     </row>
@@ -4556,9 +4391,8 @@
       <c r="E119" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="6">
-        <f>IF(D119+E119=0,"",E119/(D119+E119))</f>
-        <v/>
+      <c r="F119" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G119" s="14" t="inlineStr"/>
     </row>
@@ -4582,9 +4416,8 @@
       <c r="E120" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="11">
-        <f>IF(D120+E120=0,"",E120/(D120+E120))</f>
-        <v/>
+      <c r="F120" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G120" s="13" t="inlineStr"/>
     </row>
@@ -4608,9 +4441,8 @@
       <c r="E121" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="6">
-        <f>IF(D121+E121=0,"",E121/(D121+E121))</f>
-        <v/>
+      <c r="F121" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="14" t="inlineStr"/>
     </row>
@@ -4634,9 +4466,8 @@
       <c r="E122" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F122" s="11">
-        <f>IF(D122+E122=0,"",E122/(D122+E122))</f>
-        <v/>
+      <c r="F122" s="11" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="G122" s="13" t="inlineStr"/>
     </row>
@@ -4660,9 +4491,8 @@
       <c r="E123" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F123" s="6">
-        <f>IF(D123+E123=0,"",E123/(D123+E123))</f>
-        <v/>
+      <c r="F123" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G123" s="14" t="inlineStr"/>
     </row>
@@ -4686,9 +4516,8 @@
       <c r="E124" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F124" s="11">
-        <f>IF(D124+E124=0,"",E124/(D124+E124))</f>
-        <v/>
+      <c r="F124" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G124" s="13" t="inlineStr"/>
     </row>
@@ -4712,9 +4541,8 @@
       <c r="E125" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F125" s="6">
-        <f>IF(D125+E125=0,"",E125/(D125+E125))</f>
-        <v/>
+      <c r="F125" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G125" s="14" t="inlineStr"/>
     </row>
@@ -4738,9 +4566,8 @@
       <c r="E126" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F126" s="11">
-        <f>IF(D126+E126=0,"",E126/(D126+E126))</f>
-        <v/>
+      <c r="F126" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G126" s="13" t="inlineStr"/>
     </row>
@@ -4764,9 +4591,8 @@
       <c r="E127" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F127" s="6">
-        <f>IF(D127+E127=0,"",E127/(D127+E127))</f>
-        <v/>
+      <c r="F127" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G127" s="14" t="inlineStr"/>
     </row>
@@ -4790,9 +4616,8 @@
       <c r="E128" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="11">
-        <f>IF(D128+E128=0,"",E128/(D128+E128))</f>
-        <v/>
+      <c r="F128" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G128" s="13" t="inlineStr"/>
     </row>
@@ -4816,9 +4641,8 @@
       <c r="E129" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F129" s="6">
-        <f>IF(D129+E129=0,"",E129/(D129+E129))</f>
-        <v/>
+      <c r="F129" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G129" s="14" t="inlineStr"/>
     </row>
@@ -4842,9 +4666,8 @@
       <c r="E130" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="11">
-        <f>IF(D130+E130=0,"",E130/(D130+E130))</f>
-        <v/>
+      <c r="F130" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G130" s="13" t="inlineStr"/>
     </row>
@@ -4868,9 +4691,8 @@
       <c r="E131" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="6">
-        <f>IF(D131+E131=0,"",E131/(D131+E131))</f>
-        <v/>
+      <c r="F131" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G131" s="14" t="inlineStr"/>
     </row>
@@ -4894,9 +4716,8 @@
       <c r="E132" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F132" s="11">
-        <f>IF(D132+E132=0,"",E132/(D132+E132))</f>
-        <v/>
+      <c r="F132" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G132" s="13" t="inlineStr"/>
     </row>
@@ -4920,9 +4741,8 @@
       <c r="E133" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="6">
-        <f>IF(D133+E133=0,"",E133/(D133+E133))</f>
-        <v/>
+      <c r="F133" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G133" s="14" t="inlineStr"/>
     </row>
@@ -4946,9 +4766,8 @@
       <c r="E134" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F134" s="11">
-        <f>IF(D134+E134=0,"",E134/(D134+E134))</f>
-        <v/>
+      <c r="F134" s="11" t="n">
+        <v>0.25</v>
       </c>
       <c r="G134" s="13" t="inlineStr"/>
     </row>
@@ -4972,9 +4791,8 @@
       <c r="E135" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F135" s="6">
-        <f>IF(D135+E135=0,"",E135/(D135+E135))</f>
-        <v/>
+      <c r="F135" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G135" s="14" t="inlineStr"/>
     </row>
@@ -4998,9 +4816,8 @@
       <c r="E136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F136" s="11">
-        <f>IF(D136+E136=0,"",E136/(D136+E136))</f>
-        <v/>
+      <c r="F136" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G136" s="13" t="inlineStr"/>
     </row>
@@ -5024,9 +4841,8 @@
       <c r="E137" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F137" s="6">
-        <f>IF(D137+E137=0,"",E137/(D137+E137))</f>
-        <v/>
+      <c r="F137" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G137" s="14" t="inlineStr"/>
     </row>
@@ -5050,9 +4866,8 @@
       <c r="E138" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F138" s="11">
-        <f>IF(D138+E138=0,"",E138/(D138+E138))</f>
-        <v/>
+      <c r="F138" s="11" t="n">
+        <v>0.75</v>
       </c>
       <c r="G138" s="13" t="inlineStr"/>
     </row>
@@ -5076,9 +4891,8 @@
       <c r="E139" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F139" s="6">
-        <f>IF(D139+E139=0,"",E139/(D139+E139))</f>
-        <v/>
+      <c r="F139" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G139" s="14" t="inlineStr"/>
     </row>
@@ -5102,9 +4916,8 @@
       <c r="E140" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F140" s="11">
-        <f>IF(D140+E140=0,"",E140/(D140+E140))</f>
-        <v/>
+      <c r="F140" s="11" t="n">
+        <v>0.75</v>
       </c>
       <c r="G140" s="13" t="inlineStr"/>
     </row>
@@ -5128,9 +4941,8 @@
       <c r="E141" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F141" s="6">
-        <f>IF(D141+E141=0,"",E141/(D141+E141))</f>
-        <v/>
+      <c r="F141" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G141" s="14" t="inlineStr"/>
     </row>
@@ -5154,9 +4966,8 @@
       <c r="E142" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F142" s="11">
-        <f>IF(D142+E142=0,"",E142/(D142+E142))</f>
-        <v/>
+      <c r="F142" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G142" s="13" t="inlineStr"/>
     </row>
@@ -5180,9 +4991,8 @@
       <c r="E143" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F143" s="6">
-        <f>IF(D143+E143=0,"",E143/(D143+E143))</f>
-        <v/>
+      <c r="F143" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G143" s="14" t="inlineStr"/>
     </row>
@@ -5206,9 +5016,8 @@
       <c r="E144" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F144" s="11">
-        <f>IF(D144+E144=0,"",E144/(D144+E144))</f>
-        <v/>
+      <c r="F144" s="11" t="n">
+        <v>0.25</v>
       </c>
       <c r="G144" s="13" t="inlineStr"/>
     </row>
@@ -5232,9 +5041,8 @@
       <c r="E145" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F145" s="6">
-        <f>IF(D145+E145=0,"",E145/(D145+E145))</f>
-        <v/>
+      <c r="F145" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G145" s="14" t="inlineStr"/>
     </row>
@@ -5258,9 +5066,8 @@
       <c r="E146" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F146" s="11">
-        <f>IF(D146+E146=0,"",E146/(D146+E146))</f>
-        <v/>
+      <c r="F146" s="11" t="n">
+        <v>0.1666666666666667</v>
       </c>
       <c r="G146" s="13" t="inlineStr"/>
     </row>
@@ -5284,9 +5091,8 @@
       <c r="E147" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F147" s="6">
-        <f>IF(D147+E147=0,"",E147/(D147+E147))</f>
-        <v/>
+      <c r="F147" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G147" s="14" t="inlineStr"/>
     </row>
@@ -5310,9 +5116,8 @@
       <c r="E148" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F148" s="11">
-        <f>IF(D148+E148=0,"",E148/(D148+E148))</f>
-        <v/>
+      <c r="F148" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G148" s="13" t="inlineStr"/>
     </row>
@@ -5336,9 +5141,8 @@
       <c r="E149" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F149" s="6">
-        <f>IF(D149+E149=0,"",E149/(D149+E149))</f>
-        <v/>
+      <c r="F149" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G149" s="14" t="inlineStr"/>
     </row>
@@ -5362,9 +5166,8 @@
       <c r="E150" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F150" s="11">
-        <f>IF(D150+E150=0,"",E150/(D150+E150))</f>
-        <v/>
+      <c r="F150" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G150" s="13" t="inlineStr"/>
     </row>
@@ -5388,9 +5191,8 @@
       <c r="E151" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F151" s="6">
-        <f>IF(D151+E151=0,"",E151/(D151+E151))</f>
-        <v/>
+      <c r="F151" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G151" s="14" t="inlineStr"/>
     </row>
@@ -5414,9 +5216,8 @@
       <c r="E152" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F152" s="11">
-        <f>IF(D152+E152=0,"",E152/(D152+E152))</f>
-        <v/>
+      <c r="F152" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G152" s="13" t="inlineStr"/>
     </row>
@@ -5440,9 +5241,8 @@
       <c r="E153" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F153" s="6">
-        <f>IF(D153+E153=0,"",E153/(D153+E153))</f>
-        <v/>
+      <c r="F153" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G153" s="14" t="inlineStr"/>
     </row>
@@ -5466,9 +5266,8 @@
       <c r="E154" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F154" s="11">
-        <f>IF(D154+E154=0,"",E154/(D154+E154))</f>
-        <v/>
+      <c r="F154" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G154" s="13" t="inlineStr"/>
     </row>
@@ -5492,9 +5291,8 @@
       <c r="E155" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F155" s="6">
-        <f>IF(D155+E155=0,"",E155/(D155+E155))</f>
-        <v/>
+      <c r="F155" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G155" s="14" t="inlineStr"/>
     </row>
@@ -5518,9 +5316,8 @@
       <c r="E156" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="11">
-        <f>IF(D156+E156=0,"",E156/(D156+E156))</f>
-        <v/>
+      <c r="F156" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G156" s="13" t="inlineStr"/>
     </row>
@@ -5544,9 +5341,8 @@
       <c r="E157" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F157" s="6">
-        <f>IF(D157+E157=0,"",E157/(D157+E157))</f>
-        <v/>
+      <c r="F157" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G157" s="14" t="inlineStr"/>
     </row>
@@ -5570,9 +5366,8 @@
       <c r="E158" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F158" s="11">
-        <f>IF(D158+E158=0,"",E158/(D158+E158))</f>
-        <v/>
+      <c r="F158" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G158" s="13" t="inlineStr"/>
     </row>
@@ -5596,9 +5391,8 @@
       <c r="E159" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F159" s="6">
-        <f>IF(D159+E159=0,"",E159/(D159+E159))</f>
-        <v/>
+      <c r="F159" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G159" s="14" t="inlineStr"/>
     </row>
@@ -5622,9 +5416,8 @@
       <c r="E160" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F160" s="11">
-        <f>IF(D160+E160=0,"",E160/(D160+E160))</f>
-        <v/>
+      <c r="F160" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G160" s="13" t="inlineStr"/>
     </row>
@@ -5648,9 +5441,8 @@
       <c r="E161" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F161" s="6">
-        <f>IF(D161+E161=0,"",E161/(D161+E161))</f>
-        <v/>
+      <c r="F161" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
@@ -5678,9 +5470,8 @@
       <c r="E162" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F162" s="11">
-        <f>IF(D162+E162=0,"",E162/(D162+E162))</f>
-        <v/>
+      <c r="F162" s="11" t="n">
+        <v>0.25</v>
       </c>
       <c r="G162" s="13" t="inlineStr"/>
     </row>
@@ -5704,9 +5495,8 @@
       <c r="E163" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F163" s="6">
-        <f>IF(D163+E163=0,"",E163/(D163+E163))</f>
-        <v/>
+      <c r="F163" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G163" s="14" t="inlineStr"/>
     </row>
@@ -5730,9 +5520,8 @@
       <c r="E164" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F164" s="11">
-        <f>IF(D164+E164=0,"",E164/(D164+E164))</f>
-        <v/>
+      <c r="F164" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G164" s="13" t="inlineStr"/>
     </row>
@@ -5756,9 +5545,8 @@
       <c r="E165" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F165" s="6">
-        <f>IF(D165+E165=0,"",E165/(D165+E165))</f>
-        <v/>
+      <c r="F165" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G165" s="14" t="inlineStr"/>
     </row>
@@ -5782,9 +5570,8 @@
       <c r="E166" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F166" s="11">
-        <f>IF(D166+E166=0,"",E166/(D166+E166))</f>
-        <v/>
+      <c r="F166" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
@@ -5812,9 +5599,8 @@
       <c r="E167" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F167" s="6">
-        <f>IF(D167+E167=0,"",E167/(D167+E167))</f>
-        <v/>
+      <c r="F167" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G167" s="14" t="inlineStr"/>
     </row>
@@ -5838,9 +5624,8 @@
       <c r="E168" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F168" s="11">
-        <f>IF(D168+E168=0,"",E168/(D168+E168))</f>
-        <v/>
+      <c r="F168" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G168" s="13" t="inlineStr"/>
     </row>
@@ -5864,9 +5649,8 @@
       <c r="E169" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F169" s="6">
-        <f>IF(D169+E169=0,"",E169/(D169+E169))</f>
-        <v/>
+      <c r="F169" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G169" s="14" t="inlineStr"/>
     </row>
@@ -5890,9 +5674,8 @@
       <c r="E170" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F170" s="11">
-        <f>IF(D170+E170=0,"",E170/(D170+E170))</f>
-        <v/>
+      <c r="F170" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G170" s="13" t="inlineStr"/>
     </row>
@@ -5916,9 +5699,8 @@
       <c r="E171" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F171" s="6">
-        <f>IF(D171+E171=0,"",E171/(D171+E171))</f>
-        <v/>
+      <c r="F171" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
@@ -5946,9 +5728,8 @@
       <c r="E172" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F172" s="11">
-        <f>IF(D172+E172=0,"",E172/(D172+E172))</f>
-        <v/>
+      <c r="F172" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G172" s="13" t="inlineStr"/>
     </row>
@@ -5972,9 +5753,8 @@
       <c r="E173" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F173" s="6">
-        <f>IF(D173+E173=0,"",E173/(D173+E173))</f>
-        <v/>
+      <c r="F173" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G173" s="14" t="inlineStr"/>
     </row>
@@ -5998,9 +5778,8 @@
       <c r="E174" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F174" s="11">
-        <f>IF(D174+E174=0,"",E174/(D174+E174))</f>
-        <v/>
+      <c r="F174" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G174" s="13" t="inlineStr"/>
     </row>
@@ -6024,9 +5803,8 @@
       <c r="E175" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F175" s="6">
-        <f>IF(D175+E175=0,"",E175/(D175+E175))</f>
-        <v/>
+      <c r="F175" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G175" s="14" t="inlineStr"/>
     </row>
@@ -6050,9 +5828,8 @@
       <c r="E176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F176" s="11">
-        <f>IF(D176+E176=0,"",E176/(D176+E176))</f>
-        <v/>
+      <c r="F176" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G176" s="13" t="inlineStr"/>
     </row>
@@ -6076,9 +5853,8 @@
       <c r="E177" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F177" s="6">
-        <f>IF(D177+E177=0,"",E177/(D177+E177))</f>
-        <v/>
+      <c r="F177" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G177" s="14" t="inlineStr"/>
     </row>
@@ -6102,9 +5878,8 @@
       <c r="E178" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F178" s="11">
-        <f>IF(D178+E178=0,"",E178/(D178+E178))</f>
-        <v/>
+      <c r="F178" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G178" s="13" t="inlineStr"/>
     </row>
@@ -6128,9 +5903,8 @@
       <c r="E179" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F179" s="6">
-        <f>IF(D179+E179=0,"",E179/(D179+E179))</f>
-        <v/>
+      <c r="F179" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G179" s="14" t="inlineStr"/>
     </row>
@@ -6154,9 +5928,8 @@
       <c r="E180" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F180" s="11">
-        <f>IF(D180+E180=0,"",E180/(D180+E180))</f>
-        <v/>
+      <c r="F180" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G180" s="13" t="inlineStr"/>
     </row>
@@ -6180,9 +5953,8 @@
       <c r="E181" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F181" s="6">
-        <f>IF(D181+E181=0,"",E181/(D181+E181))</f>
-        <v/>
+      <c r="F181" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G181" s="14" t="inlineStr"/>
     </row>
@@ -6206,9 +5978,8 @@
       <c r="E182" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F182" s="11">
-        <f>IF(D182+E182=0,"",E182/(D182+E182))</f>
-        <v/>
+      <c r="F182" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G182" s="13" t="inlineStr"/>
     </row>
@@ -6232,9 +6003,8 @@
       <c r="E183" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F183" s="6">
-        <f>IF(D183+E183=0,"",E183/(D183+E183))</f>
-        <v/>
+      <c r="F183" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="G183" s="14" t="inlineStr"/>
     </row>
@@ -6258,9 +6028,8 @@
       <c r="E184" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F184" s="11">
-        <f>IF(D184+E184=0,"",E184/(D184+E184))</f>
-        <v/>
+      <c r="F184" s="11" t="n">
+        <v>0.75</v>
       </c>
       <c r="G184" s="13" t="inlineStr"/>
     </row>
@@ -6284,9 +6053,8 @@
       <c r="E185" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F185" s="6">
-        <f>IF(D185+E185=0,"",E185/(D185+E185))</f>
-        <v/>
+      <c r="F185" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G185" s="14" t="inlineStr"/>
     </row>
@@ -6310,9 +6078,8 @@
       <c r="E186" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F186" s="11">
-        <f>IF(D186+E186=0,"",E186/(D186+E186))</f>
-        <v/>
+      <c r="F186" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G186" s="13" t="inlineStr"/>
     </row>
@@ -6336,9 +6103,8 @@
       <c r="E187" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F187" s="6">
-        <f>IF(D187+E187=0,"",E187/(D187+E187))</f>
-        <v/>
+      <c r="F187" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G187" s="14" t="inlineStr"/>
     </row>
@@ -6362,9 +6128,8 @@
       <c r="E188" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F188" s="11">
-        <f>IF(D188+E188=0,"",E188/(D188+E188))</f>
-        <v/>
+      <c r="F188" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G188" s="13" t="inlineStr"/>
     </row>
@@ -6388,9 +6153,8 @@
       <c r="E189" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F189" s="6">
-        <f>IF(D189+E189=0,"",E189/(D189+E189))</f>
-        <v/>
+      <c r="F189" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G189" s="14" t="inlineStr"/>
     </row>
@@ -6414,9 +6178,8 @@
       <c r="E190" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F190" s="11">
-        <f>IF(D190+E190=0,"",E190/(D190+E190))</f>
-        <v/>
+      <c r="F190" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G190" s="13" t="inlineStr"/>
     </row>
@@ -6440,9 +6203,8 @@
       <c r="E191" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F191" s="6">
-        <f>IF(D191+E191=0,"",E191/(D191+E191))</f>
-        <v/>
+      <c r="F191" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G191" s="14" t="inlineStr"/>
     </row>
@@ -6466,9 +6228,8 @@
       <c r="E192" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F192" s="11">
-        <f>IF(D192+E192=0,"",E192/(D192+E192))</f>
-        <v/>
+      <c r="F192" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
@@ -6496,9 +6257,8 @@
       <c r="E193" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F193" s="6">
-        <f>IF(D193+E193=0,"",E193/(D193+E193))</f>
-        <v/>
+      <c r="F193" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G193" s="14" t="inlineStr"/>
     </row>
@@ -6522,9 +6282,8 @@
       <c r="E194" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F194" s="11">
-        <f>IF(D194+E194=0,"",E194/(D194+E194))</f>
-        <v/>
+      <c r="F194" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G194" s="13" t="inlineStr"/>
     </row>
@@ -6548,9 +6307,8 @@
       <c r="E195" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F195" s="6">
-        <f>IF(D195+E195=0,"",E195/(D195+E195))</f>
-        <v/>
+      <c r="F195" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -6578,9 +6336,8 @@
       <c r="E196" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F196" s="11">
-        <f>IF(D196+E196=0,"",E196/(D196+E196))</f>
-        <v/>
+      <c r="F196" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G196" s="13" t="inlineStr"/>
     </row>
@@ -6604,9 +6361,8 @@
       <c r="E197" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F197" s="6">
-        <f>IF(D197+E197=0,"",E197/(D197+E197))</f>
-        <v/>
+      <c r="F197" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -6634,9 +6390,8 @@
       <c r="E198" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F198" s="11">
-        <f>IF(D198+E198=0,"",E198/(D198+E198))</f>
-        <v/>
+      <c r="F198" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G198" s="13" t="inlineStr"/>
     </row>
@@ -6660,9 +6415,8 @@
       <c r="E199" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F199" s="6">
-        <f>IF(D199+E199=0,"",E199/(D199+E199))</f>
-        <v/>
+      <c r="F199" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G199" s="14" t="inlineStr"/>
     </row>
@@ -6686,9 +6440,8 @@
       <c r="E200" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F200" s="11">
-        <f>IF(D200+E200=0,"",E200/(D200+E200))</f>
-        <v/>
+      <c r="F200" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G200" s="13" t="inlineStr"/>
     </row>
@@ -6712,9 +6465,8 @@
       <c r="E201" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F201" s="6">
-        <f>IF(D201+E201=0,"",E201/(D201+E201))</f>
-        <v/>
+      <c r="F201" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G201" s="14" t="inlineStr"/>
     </row>
@@ -6738,9 +6490,8 @@
       <c r="E202" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F202" s="11">
-        <f>IF(D202+E202=0,"",E202/(D202+E202))</f>
-        <v/>
+      <c r="F202" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G202" s="13" t="inlineStr"/>
     </row>
@@ -6764,9 +6515,8 @@
       <c r="E203" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F203" s="6">
-        <f>IF(D203+E203=0,"",E203/(D203+E203))</f>
-        <v/>
+      <c r="F203" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G203" s="14" t="inlineStr"/>
     </row>
@@ -6790,9 +6540,8 @@
       <c r="E204" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F204" s="11">
-        <f>IF(D204+E204=0,"",E204/(D204+E204))</f>
-        <v/>
+      <c r="F204" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G204" s="13" t="inlineStr"/>
     </row>
@@ -6816,9 +6565,8 @@
       <c r="E205" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F205" s="6">
-        <f>IF(D205+E205=0,"",E205/(D205+E205))</f>
-        <v/>
+      <c r="F205" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G205" s="14" t="inlineStr"/>
     </row>
@@ -6842,9 +6590,8 @@
       <c r="E206" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F206" s="11">
-        <f>IF(D206+E206=0,"",E206/(D206+E206))</f>
-        <v/>
+      <c r="F206" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G206" s="13" t="inlineStr"/>
     </row>
@@ -6868,9 +6615,8 @@
       <c r="E207" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F207" s="6">
-        <f>IF(D207+E207=0,"",E207/(D207+E207))</f>
-        <v/>
+      <c r="F207" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G207" s="14" t="inlineStr"/>
     </row>
@@ -6894,9 +6640,8 @@
       <c r="E208" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F208" s="11">
-        <f>IF(D208+E208=0,"",E208/(D208+E208))</f>
-        <v/>
+      <c r="F208" s="11" t="n">
+        <v>0.5714285714285714</v>
       </c>
       <c r="G208" s="13" t="inlineStr"/>
     </row>
@@ -6920,9 +6665,8 @@
       <c r="E209" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F209" s="6">
-        <f>IF(D209+E209=0,"",E209/(D209+E209))</f>
-        <v/>
+      <c r="F209" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G209" s="14" t="inlineStr"/>
     </row>
@@ -6946,9 +6690,8 @@
       <c r="E210" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F210" s="11">
-        <f>IF(D210+E210=0,"",E210/(D210+E210))</f>
-        <v/>
+      <c r="F210" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G210" s="13" t="inlineStr"/>
     </row>
@@ -6972,9 +6715,8 @@
       <c r="E211" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F211" s="6">
-        <f>IF(D211+E211=0,"",E211/(D211+E211))</f>
-        <v/>
+      <c r="F211" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G211" s="14" t="inlineStr">
         <is>
@@ -7002,9 +6744,8 @@
       <c r="E212" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F212" s="11">
-        <f>IF(D212+E212=0,"",E212/(D212+E212))</f>
-        <v/>
+      <c r="F212" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G212" s="13" t="inlineStr"/>
     </row>
@@ -7028,9 +6769,8 @@
       <c r="E213" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F213" s="6">
-        <f>IF(D213+E213=0,"",E213/(D213+E213))</f>
-        <v/>
+      <c r="F213" s="6" t="n">
+        <v>0.4</v>
       </c>
       <c r="G213" s="14" t="inlineStr"/>
     </row>
@@ -7054,9 +6794,8 @@
       <c r="E214" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F214" s="11">
-        <f>IF(D214+E214=0,"",E214/(D214+E214))</f>
-        <v/>
+      <c r="F214" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
@@ -7084,9 +6823,8 @@
       <c r="E215" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F215" s="6">
-        <f>IF(D215+E215=0,"",E215/(D215+E215))</f>
-        <v/>
+      <c r="F215" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G215" s="14" t="inlineStr"/>
     </row>
@@ -7110,9 +6848,8 @@
       <c r="E216" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F216" s="11">
-        <f>IF(D216+E216=0,"",E216/(D216+E216))</f>
-        <v/>
+      <c r="F216" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G216" s="13" t="inlineStr"/>
     </row>
@@ -7136,9 +6873,8 @@
       <c r="E217" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F217" s="6">
-        <f>IF(D217+E217=0,"",E217/(D217+E217))</f>
-        <v/>
+      <c r="F217" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G217" s="14" t="inlineStr"/>
     </row>
@@ -7162,9 +6898,8 @@
       <c r="E218" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F218" s="11">
-        <f>IF(D218+E218=0,"",E218/(D218+E218))</f>
-        <v/>
+      <c r="F218" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
     </row>
@@ -7188,9 +6923,8 @@
       <c r="E219" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F219" s="6">
-        <f>IF(D219+E219=0,"",E219/(D219+E219))</f>
-        <v/>
+      <c r="F219" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -7218,9 +6952,8 @@
       <c r="E220" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F220" s="11">
-        <f>IF(D220+E220=0,"",E220/(D220+E220))</f>
-        <v/>
+      <c r="F220" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
@@ -7248,9 +6981,8 @@
       <c r="E221" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F221" s="6">
-        <f>IF(D221+E221=0,"",E221/(D221+E221))</f>
-        <v/>
+      <c r="F221" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G221" s="14" t="inlineStr"/>
     </row>
@@ -7274,9 +7006,8 @@
       <c r="E222" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F222" s="11">
-        <f>IF(D222+E222=0,"",E222/(D222+E222))</f>
-        <v/>
+      <c r="F222" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
     </row>
@@ -7300,9 +7031,8 @@
       <c r="E223" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F223" s="6">
-        <f>IF(D223+E223=0,"",E223/(D223+E223))</f>
-        <v/>
+      <c r="F223" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G223" s="14" t="inlineStr"/>
     </row>
@@ -7326,9 +7056,8 @@
       <c r="E224" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F224" s="11">
-        <f>IF(D224+E224=0,"",E224/(D224+E224))</f>
-        <v/>
+      <c r="F224" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
     </row>
@@ -7352,9 +7081,8 @@
       <c r="E225" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F225" s="6">
-        <f>IF(D225+E225=0,"",E225/(D225+E225))</f>
-        <v/>
+      <c r="F225" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G225" s="14" t="inlineStr">
         <is>
@@ -7382,9 +7110,8 @@
       <c r="E226" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F226" s="11">
-        <f>IF(D226+E226=0,"",E226/(D226+E226))</f>
-        <v/>
+      <c r="F226" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
     </row>
@@ -7408,9 +7135,8 @@
       <c r="E227" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F227" s="6">
-        <f>IF(D227+E227=0,"",E227/(D227+E227))</f>
-        <v/>
+      <c r="F227" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G227" s="14" t="inlineStr"/>
     </row>
@@ -7434,9 +7160,8 @@
       <c r="E228" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F228" s="11">
-        <f>IF(D228+E228=0,"",E228/(D228+E228))</f>
-        <v/>
+      <c r="F228" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -7464,9 +7189,8 @@
       <c r="E229" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F229" s="6">
-        <f>IF(D229+E229=0,"",E229/(D229+E229))</f>
-        <v/>
+      <c r="F229" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
@@ -7494,9 +7218,8 @@
       <c r="E230" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F230" s="11">
-        <f>IF(D230+E230=0,"",E230/(D230+E230))</f>
-        <v/>
+      <c r="F230" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
     </row>
@@ -7520,9 +7243,8 @@
       <c r="E231" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F231" s="6">
-        <f>IF(D231+E231=0,"",E231/(D231+E231))</f>
-        <v/>
+      <c r="F231" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G231" s="14" t="inlineStr"/>
     </row>
@@ -7638,9 +7360,8 @@
       <c r="E5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="6">
-        <f>IF(D5+E5=0,"",E5/(D5+E5))</f>
-        <v/>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>3</v>
@@ -7667,9 +7388,8 @@
       <c r="E6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="11">
-        <f>IF(D6+E6=0,"",E6/(D6+E6))</f>
-        <v/>
+      <c r="F6" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>3</v>
@@ -7696,9 +7416,8 @@
       <c r="E7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="6">
-        <f>IF(D7+E7=0,"",E7/(D7+E7))</f>
-        <v/>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>2</v>
@@ -7725,9 +7444,8 @@
       <c r="E8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="11">
-        <f>IF(D8+E8=0,"",E8/(D8+E8))</f>
-        <v/>
+      <c r="F8" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>2</v>
@@ -7754,9 +7472,8 @@
       <c r="E9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="6">
-        <f>IF(D9+E9=0,"",E9/(D9+E9))</f>
-        <v/>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>2</v>
@@ -7783,9 +7500,8 @@
       <c r="E10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="11">
-        <f>IF(D10+E10=0,"",E10/(D10+E10))</f>
-        <v/>
+      <c r="F10" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>2</v>
@@ -7812,9 +7528,8 @@
       <c r="E11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="6">
-        <f>IF(D11+E11=0,"",E11/(D11+E11))</f>
-        <v/>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>2</v>
@@ -7841,9 +7556,8 @@
       <c r="E12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="11">
-        <f>IF(D12+E12=0,"",E12/(D12+E12))</f>
-        <v/>
+      <c r="F12" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>2</v>
@@ -7870,9 +7584,8 @@
       <c r="E13" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="6">
-        <f>IF(D13+E13=0,"",E13/(D13+E13))</f>
-        <v/>
+      <c r="F13" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>2</v>
@@ -7899,9 +7612,8 @@
       <c r="E14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="11">
-        <f>IF(D14+E14=0,"",E14/(D14+E14))</f>
-        <v/>
+      <c r="F14" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>2</v>
@@ -7932,9 +7644,8 @@
       <c r="E15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="6">
-        <f>IF(D15+E15=0,"",E15/(D15+E15))</f>
-        <v/>
+      <c r="F15" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>1</v>
@@ -7961,9 +7672,8 @@
       <c r="E16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="11">
-        <f>IF(D16+E16=0,"",E16/(D16+E16))</f>
-        <v/>
+      <c r="F16" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>1</v>
@@ -7994,9 +7704,8 @@
       <c r="E17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="6">
-        <f>IF(D17+E17=0,"",E17/(D17+E17))</f>
-        <v/>
+      <c r="F17" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>1</v>
@@ -8023,9 +7732,8 @@
       <c r="E18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="11">
-        <f>IF(D18+E18=0,"",E18/(D18+E18))</f>
-        <v/>
+      <c r="F18" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>1</v>
@@ -8052,9 +7760,8 @@
       <c r="E19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="6">
-        <f>IF(D19+E19=0,"",E19/(D19+E19))</f>
-        <v/>
+      <c r="F19" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>1</v>
@@ -8081,9 +7788,8 @@
       <c r="E20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="11">
-        <f>IF(D20+E20=0,"",E20/(D20+E20))</f>
-        <v/>
+      <c r="F20" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>1</v>
@@ -8110,9 +7816,8 @@
       <c r="E21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="6">
-        <f>IF(D21+E21=0,"",E21/(D21+E21))</f>
-        <v/>
+      <c r="F21" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>1</v>
@@ -8139,9 +7844,8 @@
       <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="11">
-        <f>IF(D22+E22=0,"",E22/(D22+E22))</f>
-        <v/>
+      <c r="F22" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>1</v>
@@ -8168,9 +7872,8 @@
       <c r="E23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="6">
-        <f>IF(D23+E23=0,"",E23/(D23+E23))</f>
-        <v/>
+      <c r="F23" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>1</v>
@@ -8197,9 +7900,8 @@
       <c r="E24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11">
-        <f>IF(D24+E24=0,"",E24/(D24+E24))</f>
-        <v/>
+      <c r="F24" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>1</v>
@@ -8226,9 +7928,8 @@
       <c r="E25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="6">
-        <f>IF(D25+E25=0,"",E25/(D25+E25))</f>
-        <v/>
+      <c r="F25" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>1</v>
@@ -8255,9 +7956,8 @@
       <c r="E26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="11">
-        <f>IF(D26+E26=0,"",E26/(D26+E26))</f>
-        <v/>
+      <c r="F26" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>1</v>
@@ -8284,9 +7984,8 @@
       <c r="E27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="6">
-        <f>IF(D27+E27=0,"",E27/(D27+E27))</f>
-        <v/>
+      <c r="F27" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
@@ -8313,9 +8012,8 @@
       <c r="E28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="11">
-        <f>IF(D28+E28=0,"",E28/(D28+E28))</f>
-        <v/>
+      <c r="F28" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>1</v>
@@ -8342,9 +8040,8 @@
       <c r="E29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="6">
-        <f>IF(D29+E29=0,"",E29/(D29+E29))</f>
-        <v/>
+      <c r="F29" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>1</v>
@@ -8371,9 +8068,8 @@
       <c r="E30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11">
-        <f>IF(D30+E30=0,"",E30/(D30+E30))</f>
-        <v/>
+      <c r="F30" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>1</v>
@@ -8404,9 +8100,8 @@
       <c r="E31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="6">
-        <f>IF(D31+E31=0,"",E31/(D31+E31))</f>
-        <v/>
+      <c r="F31" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>1</v>
@@ -8433,9 +8128,8 @@
       <c r="E32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="11">
-        <f>IF(D32+E32=0,"",E32/(D32+E32))</f>
-        <v/>
+      <c r="F32" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1</v>
@@ -8466,9 +8160,8 @@
       <c r="E33" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="6">
-        <f>IF(D33+E33=0,"",E33/(D33+E33))</f>
-        <v/>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>1</v>
@@ -8499,9 +8192,8 @@
       <c r="E34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="11">
-        <f>IF(D34+E34=0,"",E34/(D34+E34))</f>
-        <v/>
+      <c r="F34" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1</v>
@@ -8532,9 +8224,8 @@
       <c r="E35" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="6">
-        <f>IF(D35+E35=0,"",E35/(D35+E35))</f>
-        <v/>
+      <c r="F35" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>1</v>
@@ -8561,9 +8252,8 @@
       <c r="E36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="11">
-        <f>IF(D36+E36=0,"",E36/(D36+E36))</f>
-        <v/>
+      <c r="F36" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1</v>
@@ -8594,9 +8284,8 @@
       <c r="E37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="6">
-        <f>IF(D37+E37=0,"",E37/(D37+E37))</f>
-        <v/>
+      <c r="F37" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>1</v>
@@ -8623,9 +8312,8 @@
       <c r="E38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="11">
-        <f>IF(D38+E38=0,"",E38/(D38+E38))</f>
-        <v/>
+      <c r="F38" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>1</v>
@@ -8656,9 +8344,8 @@
       <c r="E39" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="6">
-        <f>IF(D39+E39=0,"",E39/(D39+E39))</f>
-        <v/>
+      <c r="F39" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
@@ -8689,9 +8376,8 @@
       <c r="E40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11">
-        <f>IF(D40+E40=0,"",E40/(D40+E40))</f>
-        <v/>
+      <c r="F40" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>1</v>
@@ -8722,9 +8408,8 @@
       <c r="E41" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="6">
-        <f>IF(D41+E41=0,"",E41/(D41+E41))</f>
-        <v/>
+      <c r="F41" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
@@ -8755,9 +8440,8 @@
       <c r="E42" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="F42" s="11">
-        <f>IF(D42+E42=0,"",E42/(D42+E42))</f>
-        <v/>
+      <c r="F42" s="11" t="n">
+        <v>0.9285714285714286</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>6</v>
@@ -8784,9 +8468,8 @@
       <c r="E43" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F43" s="6">
-        <f>IF(D43+E43=0,"",E43/(D43+E43))</f>
-        <v/>
+      <c r="F43" s="6" t="n">
+        <v>0.7692307692307693</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>8</v>
@@ -8813,9 +8496,8 @@
       <c r="E44" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="11">
-        <f>IF(D44+E44=0,"",E44/(D44+E44))</f>
-        <v/>
+      <c r="F44" s="11" t="n">
+        <v>0.75</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>4</v>
@@ -8842,9 +8524,8 @@
       <c r="E45" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="6">
-        <f>IF(D45+E45=0,"",E45/(D45+E45))</f>
-        <v/>
+      <c r="F45" s="6" t="n">
+        <v>0.75</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>4</v>
@@ -8871,9 +8552,8 @@
       <c r="E46" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="11">
-        <f>IF(D46+E46=0,"",E46/(D46+E46))</f>
-        <v/>
+      <c r="F46" s="11" t="n">
+        <v>0.75</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>4</v>
@@ -8900,9 +8580,8 @@
       <c r="E47" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="6">
-        <f>IF(D47+E47=0,"",E47/(D47+E47))</f>
-        <v/>
+      <c r="F47" s="6" t="n">
+        <v>0.7142857142857143</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>4</v>
@@ -8929,9 +8608,8 @@
       <c r="E48" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F48" s="11">
-        <f>IF(D48+E48=0,"",E48/(D48+E48))</f>
-        <v/>
+      <c r="F48" s="11" t="n">
+        <v>0.7142857142857143</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>5</v>
@@ -8958,9 +8636,8 @@
       <c r="E49" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="F49" s="6">
-        <f>IF(D49+E49=0,"",E49/(D49+E49))</f>
-        <v/>
+      <c r="F49" s="6" t="n">
+        <v>0.6857142857142857</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>11</v>
@@ -8987,9 +8664,8 @@
       <c r="E50" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="11">
-        <f>IF(D50+E50=0,"",E50/(D50+E50))</f>
-        <v/>
+      <c r="F50" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>2</v>
@@ -9016,9 +8692,8 @@
       <c r="E51" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="6">
-        <f>IF(D51+E51=0,"",E51/(D51+E51))</f>
-        <v/>
+      <c r="F51" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>2</v>
@@ -9049,9 +8724,8 @@
       <c r="E52" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="F52" s="11">
-        <f>IF(D52+E52=0,"",E52/(D52+E52))</f>
-        <v/>
+      <c r="F52" s="11" t="n">
+        <v>0.6</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>12</v>
@@ -9078,9 +8752,8 @@
       <c r="E53" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F53" s="6">
-        <f>IF(D53+E53=0,"",E53/(D53+E53))</f>
-        <v/>
+      <c r="F53" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>3</v>
@@ -9107,9 +8780,8 @@
       <c r="E54" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F54" s="11">
-        <f>IF(D54+E54=0,"",E54/(D54+E54))</f>
-        <v/>
+      <c r="F54" s="11" t="n">
+        <v>0.5714285714285714</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>8</v>
@@ -9136,9 +8808,8 @@
       <c r="E55" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F55" s="6">
-        <f>IF(D55+E55=0,"",E55/(D55+E55))</f>
-        <v/>
+      <c r="F55" s="6" t="n">
+        <v>0.5714285714285714</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>9</v>
@@ -9165,9 +8836,8 @@
       <c r="E56" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F56" s="11">
-        <f>IF(D56+E56=0,"",E56/(D56+E56))</f>
-        <v/>
+      <c r="F56" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>7</v>
@@ -9194,9 +8864,8 @@
       <c r="E57" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="6">
-        <f>IF(D57+E57=0,"",E57/(D57+E57))</f>
-        <v/>
+      <c r="F57" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>2</v>
@@ -9223,9 +8892,8 @@
       <c r="E58" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="11">
-        <f>IF(D58+E58=0,"",E58/(D58+E58))</f>
-        <v/>
+      <c r="F58" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>2</v>
@@ -9252,9 +8920,8 @@
       <c r="E59" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="6">
-        <f>IF(D59+E59=0,"",E59/(D59+E59))</f>
-        <v/>
+      <c r="F59" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>2</v>
@@ -9281,9 +8948,8 @@
       <c r="E60" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11">
-        <f>IF(D60+E60=0,"",E60/(D60+E60))</f>
-        <v/>
+      <c r="F60" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>1</v>
@@ -9310,9 +8976,8 @@
       <c r="E61" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="F61" s="6">
-        <f>IF(D61+E61=0,"",E61/(D61+E61))</f>
-        <v/>
+      <c r="F61" s="6" t="n">
+        <v>0.4782608695652174</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>9</v>
@@ -9339,9 +9004,8 @@
       <c r="E62" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F62" s="11">
-        <f>IF(D62+E62=0,"",E62/(D62+E62))</f>
-        <v/>
+      <c r="F62" s="11" t="n">
+        <v>0.4594594594594595</v>
       </c>
       <c r="G62" s="13" t="n">
         <v>12</v>
@@ -9368,9 +9032,8 @@
       <c r="E63" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="F63" s="6">
-        <f>IF(D63+E63=0,"",E63/(D63+E63))</f>
-        <v/>
+      <c r="F63" s="6" t="n">
+        <v>0.4339622641509434</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>12</v>
@@ -9397,9 +9060,8 @@
       <c r="E64" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F64" s="11">
-        <f>IF(D64+E64=0,"",E64/(D64+E64))</f>
-        <v/>
+      <c r="F64" s="11" t="n">
+        <v>0.4285714285714285</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>8</v>
@@ -9426,9 +9088,8 @@
       <c r="E65" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F65" s="6">
-        <f>IF(D65+E65=0,"",E65/(D65+E65))</f>
-        <v/>
+      <c r="F65" s="6" t="n">
+        <v>0.3846153846153846</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>6</v>
@@ -9455,9 +9116,8 @@
       <c r="E66" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F66" s="11">
-        <f>IF(D66+E66=0,"",E66/(D66+E66))</f>
-        <v/>
+      <c r="F66" s="11" t="n">
+        <v>0.3571428571428572</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>7</v>
@@ -9484,9 +9144,8 @@
       <c r="E67" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="6">
-        <f>IF(D67+E67=0,"",E67/(D67+E67))</f>
-        <v/>
+      <c r="F67" s="6" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>2</v>
@@ -9513,9 +9172,8 @@
       <c r="E68" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="11">
-        <f>IF(D68+E68=0,"",E68/(D68+E68))</f>
-        <v/>
+      <c r="F68" s="11" t="n">
+        <v>0.2777777777777778</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>8</v>
@@ -9542,9 +9200,8 @@
       <c r="E69" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="6">
-        <f>IF(D69+E69=0,"",E69/(D69+E69))</f>
-        <v/>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>4</v>
@@ -9571,9 +9228,8 @@
       <c r="E70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="11">
-        <f>IF(D70+E70=0,"",E70/(D70+E70))</f>
-        <v/>
+      <c r="F70" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G70" s="13" t="n">
         <v>2</v>
@@ -9600,9 +9256,8 @@
       <c r="E71" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="6">
-        <f>IF(D71+E71=0,"",E71/(D71+E71))</f>
-        <v/>
+      <c r="F71" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>2</v>
@@ -9629,9 +9284,8 @@
       <c r="E72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="11">
-        <f>IF(D72+E72=0,"",E72/(D72+E72))</f>
-        <v/>
+      <c r="F72" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>1</v>
@@ -9658,9 +9312,8 @@
       <c r="E73" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="6">
-        <f>IF(D73+E73=0,"",E73/(D73+E73))</f>
-        <v/>
+      <c r="F73" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>1</v>
@@ -9687,9 +9340,8 @@
       <c r="E74" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="11">
-        <f>IF(D74+E74=0,"",E74/(D74+E74))</f>
-        <v/>
+      <c r="F74" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>1</v>
@@ -9716,9 +9368,8 @@
       <c r="E75" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="6">
-        <f>IF(D75+E75=0,"",E75/(D75+E75))</f>
-        <v/>
+      <c r="F75" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>1</v>
@@ -9745,9 +9396,8 @@
       <c r="E76" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="11">
-        <f>IF(D76+E76=0,"",E76/(D76+E76))</f>
-        <v/>
+      <c r="F76" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>1</v>
@@ -9774,9 +9424,8 @@
       <c r="E77" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="6">
-        <f>IF(D77+E77=0,"",E77/(D77+E77))</f>
-        <v/>
+      <c r="F77" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G77" s="14" t="n">
         <v>1</v>
@@ -9803,9 +9452,8 @@
       <c r="E78" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="11">
-        <f>IF(D78+E78=0,"",E78/(D78+E78))</f>
-        <v/>
+      <c r="F78" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G78" s="13" t="n">
         <v>1</v>
@@ -9832,9 +9480,8 @@
       <c r="E79" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="6">
-        <f>IF(D79+E79=0,"",E79/(D79+E79))</f>
-        <v/>
+      <c r="F79" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>1</v>
@@ -9861,9 +9508,8 @@
       <c r="E80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="11">
-        <f>IF(D80+E80=0,"",E80/(D80+E80))</f>
-        <v/>
+      <c r="F80" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>1</v>
@@ -9890,9 +9536,8 @@
       <c r="E81" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="6">
-        <f>IF(D81+E81=0,"",E81/(D81+E81))</f>
-        <v/>
+      <c r="F81" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>1</v>
@@ -9906,21 +9551,17 @@
         </is>
       </c>
       <c r="B82" s="20" t="n"/>
-      <c r="C82" s="20">
-        <f>SUM(C5:C81)</f>
-        <v/>
-      </c>
-      <c r="D82" s="20">
-        <f>SUM(D5:D81)</f>
-        <v/>
-      </c>
-      <c r="E82" s="20">
-        <f>SUM(E5:E81)</f>
-        <v/>
-      </c>
-      <c r="F82" s="18">
-        <f>E82/(D82+E82)</f>
-        <v/>
+      <c r="C82" s="20" t="n">
+        <v>437</v>
+      </c>
+      <c r="D82" s="20" t="n">
+        <v>185</v>
+      </c>
+      <c r="E82" s="20" t="n">
+        <v>251</v>
+      </c>
+      <c r="F82" s="18" t="n">
+        <v>0.5756880733944955</v>
       </c>
       <c r="G82" s="20" t="n"/>
       <c r="H82" s="20" t="n"/>
@@ -9993,9 +9634,8 @@
       <c r="E87" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="F87" s="6">
-        <f>IF(D87+E87=0,"",E87/(D87+E87))</f>
-        <v/>
+      <c r="F87" s="6" t="n">
+        <v>0.4814814814814815</v>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
@@ -10018,9 +9658,8 @@
       <c r="E88" s="13" t="n">
         <v>106</v>
       </c>
-      <c r="F88" s="11">
-        <f>IF(D88+E88=0,"",E88/(D88+E88))</f>
-        <v/>
+      <c r="F88" s="11" t="n">
+        <v>0.7066666666666667</v>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
@@ -10043,9 +9682,8 @@
       <c r="E89" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F89" s="6">
-        <f>IF(D89+E89=0,"",E89/(D89+E89))</f>
-        <v/>
+      <c r="F89" s="6" t="n">
+        <v>0.9375</v>
       </c>
     </row>
   </sheetData>
@@ -10186,9 +9824,8 @@
         <v>1</v>
       </c>
       <c r="I5" s="14" t="n"/>
-      <c r="J5" s="6">
-        <f>IF(B5=0,"",C5/B5)</f>
-        <v/>
+      <c r="J5" s="6" t="n">
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -10217,9 +9854,8 @@
       <c r="I6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="11">
-        <f>IF(B6=0,"",C6/B6)</f>
-        <v/>
+      <c r="J6" s="11" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -10250,9 +9886,8 @@
       <c r="I7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="6">
-        <f>IF(B7=0,"",C7/B7)</f>
-        <v/>
+      <c r="J7" s="6" t="n">
+        <v>0.5789473684210527</v>
       </c>
     </row>
     <row r="8">
@@ -10279,9 +9914,8 @@
       </c>
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="n"/>
-      <c r="J8" s="11">
-        <f>IF(B8=0,"",C8/B8)</f>
-        <v/>
+      <c r="J8" s="11" t="n">
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -10310,9 +9944,8 @@
         <v>2</v>
       </c>
       <c r="I9" s="14" t="n"/>
-      <c r="J9" s="6">
-        <f>IF(B9=0,"",C9/B9)</f>
-        <v/>
+      <c r="J9" s="6" t="n">
+        <v>0.3181818181818182</v>
       </c>
     </row>
     <row r="10">
@@ -10343,9 +9976,8 @@
         <v>2</v>
       </c>
       <c r="I10" s="13" t="n"/>
-      <c r="J10" s="11">
-        <f>IF(B10=0,"",C10/B10)</f>
-        <v/>
+      <c r="J10" s="11" t="n">
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="11">
@@ -10374,9 +10006,8 @@
       </c>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
-      <c r="J11" s="6">
-        <f>IF(B11=0,"",C11/B11)</f>
-        <v/>
+      <c r="J11" s="6" t="n">
+        <v>0.65625</v>
       </c>
     </row>
     <row r="12">
@@ -10407,9 +10038,8 @@
         <v>2</v>
       </c>
       <c r="I12" s="13" t="n"/>
-      <c r="J12" s="11">
-        <f>IF(B12=0,"",C12/B12)</f>
-        <v/>
+      <c r="J12" s="11" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -10418,41 +10048,32 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="B13" s="20">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="20">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="20">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="20">
-        <f>SUM(E5:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="20">
-        <f>SUM(F5:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="20">
-        <f>SUM(G5:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="20">
-        <f>SUM(H5:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="20">
-        <f>SUM(I5:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="18">
-        <f>C13/B13</f>
-        <v/>
+      <c r="B13" s="20" t="n">
+        <v>181</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>87</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.4806629834254144</v>
       </c>
     </row>
   </sheetData>
@@ -34968,6 +34589,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -35124,15 +34746,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Percentages are live formulas</t>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>Percentages and totals are computed values</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Every % and total in this workbook is a formula over the counts beside it, not a pasted number, so the sheets stay correct if you filter or edit the underlying rows. They carry no cached result — Excel and Google Sheets compute them the moment the file opens. A lightweight preview pane that reads only cached values may show those cells blank until you open the file properly; that is the preview, not the workbook.</t>
+          <t>Every % and total in this workbook is a stored number, not a live formula. They were originally written as formulas, but openpyxl cannot write a cached result alongside a formula, and any viewer that reads cached values rather than recalculating - Google Drive preview, Quick Look, Numbers, mobile Excel - rendered those cells as 0. Storing the computed value makes the workbook read correctly everywhere. The trade-off is that these cells will NOT update if you edit or filter the rows beneath them; recompute by hand, or ask for a formula-driven copy if you need one that recalculates.</t>
         </is>
       </c>
     </row>

--- a/KTU-consultation-analysis.xlsx
+++ b/KTU-consultation-analysis.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,24 @@
       <color rgb="FFA32833"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1C5566"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <color rgb="FF1F2933"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F2933"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF6B7688"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -181,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -199,11 +217,16 @@
         <color rgb="FF1C5566"/>
       </top>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFD3DAE0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,6 +317,20 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="21" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="21" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1453,10 +1490,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1476,9 +1513,9 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Same scope and exclusions as sheet 1. Sorted by month, then by cancellations. "Cancellation %" is blank where a town had no resolved appointment that month. Use this sheet as the source for a pivot table: Month on columns, Town on rows.</t>
+      <c r="A2" s="56" t="inlineStr">
+        <is>
+          <t>Same scope and exclusions as sheet 1. Grouped by month: each block opens with the month name, lists its towns sorted by cancellations, and closes with a bold month subtotal. Use the outline handles in the left margin to collapse the town detail and read month totals only. Cancellation % is blank where a town had no resolved appointment that month.</t>
         </is>
       </c>
     </row>
@@ -1520,5733 +1557,6238 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>September 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="n"/>
+      <c r="C5" s="58" t="n"/>
+      <c r="D5" s="58" t="n"/>
+      <c r="E5" s="58" t="n"/>
+      <c r="F5" s="58" t="n"/>
+      <c r="G5" s="58" t="n"/>
+    </row>
+    <row r="6" outlineLevel="1">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Belleville</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="n">
+      <c r="C6" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="E6" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="59" t="n"/>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C7" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="D7" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="13" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="G7" s="59" t="n"/>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Irvington</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14" t="n">
+      <c r="C8" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="E8" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="59" t="n"/>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Lake Hiawatha</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="13" t="n">
+      <c r="C9" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="E9" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="59" t="n"/>
+    </row>
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Monroeville</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="n">
+      <c r="C10" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="E10" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="59" t="n"/>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C11" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="D11" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="G11" s="59" t="n"/>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C12" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D12" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E12" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="G12" s="59" t="n"/>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13" t="n">
+      <c r="C13" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F13" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="G13" s="59" t="n"/>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Forked River</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="14" t="n">
+      <c r="C14" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="G14" s="59" t="n"/>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="13" t="n">
+      <c r="C15" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F15" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="G15" s="59" t="n"/>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Short Hills</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="n">
+      <c r="C16" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F16" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="G16" s="59" t="n"/>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="n">
+      <c r="C17" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F17" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="G17" s="59" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B18" s="62" t="inlineStr">
+        <is>
+          <t>12 towns</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="64" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="62" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>October 2025</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="58" t="n"/>
+    </row>
+    <row r="21" outlineLevel="1">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C21" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D21" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E21" s="60" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F21" s="61" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G17" s="14" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="G21" s="59" t="n"/>
+    </row>
+    <row r="22" outlineLevel="1">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C22" s="60" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13" t="n">
+      <c r="D22" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F22" s="61" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="G18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="G22" s="59" t="n"/>
+    </row>
+    <row r="23" outlineLevel="1">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C23" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D23" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E23" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F23" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="G23" s="59" t="n"/>
+    </row>
+    <row r="24" outlineLevel="1">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C24" s="60" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D24" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E24" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F24" s="61" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="G20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="G24" s="59" t="n"/>
+    </row>
+    <row r="25" outlineLevel="1">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>North Caldwell</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C25" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D25" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E25" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="F25" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="59" t="n"/>
+    </row>
+    <row r="26" outlineLevel="1">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>Wayne</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C26" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D26" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E26" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="F26" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="59" t="n"/>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C27" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="6" t="n">
+      <c r="D27" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G23" s="14" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="G27" s="59" t="n"/>
+    </row>
+    <row r="28" outlineLevel="1">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="n">
+      <c r="C28" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="E28" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="59" t="n"/>
+    </row>
+    <row r="29" outlineLevel="1">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C29" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="6" t="n">
+      <c r="D29" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G25" s="14" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="G29" s="59" t="n"/>
+    </row>
+    <row r="30" outlineLevel="1">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Montcalir</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="n">
+      <c r="C30" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="E30" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="59" t="n"/>
+    </row>
+    <row r="31" outlineLevel="1">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>Morris Plains</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14" t="n">
+      <c r="C31" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="E31" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="59" t="n"/>
+    </row>
+    <row r="32" outlineLevel="1">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B32" s="59" t="inlineStr">
         <is>
           <t>Newark</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="n">
+      <c r="C32" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="E32" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="59" t="n"/>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14" t="n">
+      <c r="C33" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="E33" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="59" t="n"/>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="A34" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="n">
+      <c r="C34" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="E34" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="59" t="n"/>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t>Roseland</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C35" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="6" t="n">
+      <c r="D35" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G31" s="14" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="G35" s="59" t="n"/>
+    </row>
+    <row r="36" outlineLevel="1">
+      <c r="A36" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B36" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="13" t="n">
+      <c r="C36" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="E36" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="59" t="n"/>
+    </row>
+    <row r="37" outlineLevel="1">
+      <c r="A37" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B37" s="59" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14" t="n">
+      <c r="C37" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="E37" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="59" t="n"/>
+    </row>
+    <row r="38" outlineLevel="1">
+      <c r="A38" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C38" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="11" t="n">
+      <c r="D38" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="G38" s="59" t="n"/>
+    </row>
+    <row r="39" outlineLevel="1">
+      <c r="A39" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C39" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D39" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E39" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F39" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="14" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="G39" s="59" t="n"/>
+    </row>
+    <row r="40" outlineLevel="1">
+      <c r="A40" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B40" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="13" t="n">
+      <c r="C40" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F40" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="13" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="G40" s="59" t="n"/>
+    </row>
+    <row r="41" outlineLevel="1">
+      <c r="A41" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B41" s="59" t="inlineStr">
         <is>
           <t>Chatham</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="14" t="n">
+      <c r="C41" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F41" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="14" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="G41" s="59" t="n"/>
+    </row>
+    <row r="42" outlineLevel="1">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B42" s="59" t="inlineStr">
         <is>
           <t>Lyndhurst</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="13" t="n">
+      <c r="C42" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F42" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="13" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="G42" s="59" t="n"/>
+    </row>
+    <row r="43" outlineLevel="1">
+      <c r="A43" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B43" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="14" t="n">
+      <c r="C43" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F43" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="14" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="G43" s="59" t="n"/>
+    </row>
+    <row r="44" outlineLevel="1">
+      <c r="A44" s="59" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>West Caldwell</t>
         </is>
       </c>
-      <c r="C40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="n">
+      <c r="C44" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="13" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="F44" s="61" t="n"/>
+      <c r="G44" s="59" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>24 towns</t>
+        </is>
+      </c>
+      <c r="C45" s="63" t="n">
+        <v>58</v>
+      </c>
+      <c r="D45" s="63" t="n">
+        <v>22</v>
+      </c>
+      <c r="E45" s="63" t="n">
+        <v>35</v>
+      </c>
+      <c r="F45" s="64" t="n">
+        <v>0.6140350877192983</v>
+      </c>
+      <c r="G45" s="62" t="inlineStr"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="57" t="inlineStr">
+        <is>
+          <t>November 2025</t>
+        </is>
+      </c>
+      <c r="B47" s="58" t="n"/>
+      <c r="C47" s="58" t="n"/>
+      <c r="D47" s="58" t="n"/>
+      <c r="E47" s="58" t="n"/>
+      <c r="F47" s="58" t="n"/>
+      <c r="G47" s="58" t="n"/>
+    </row>
+    <row r="48" outlineLevel="1">
+      <c r="A48" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B48" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C48" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D48" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="14" t="n">
+      <c r="E48" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F48" s="61" t="n">
         <v>0.625</v>
       </c>
-      <c r="G41" s="14" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="G48" s="59" t="n"/>
+    </row>
+    <row r="49" outlineLevel="1">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B49" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C42" s="13" t="n">
+      <c r="C49" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D49" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E49" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="F49" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="59" t="n"/>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="A50" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B50" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C50" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="14" t="n">
+      <c r="D50" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F50" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G43" s="14" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="G50" s="59" t="n"/>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="A51" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B51" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C44" s="13" t="n">
+      <c r="C51" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D51" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E51" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="F51" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="59" t="n"/>
+    </row>
+    <row r="52" outlineLevel="1">
+      <c r="A52" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B52" s="59" t="inlineStr">
         <is>
           <t>Chatham</t>
         </is>
       </c>
-      <c r="C45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="14" t="n">
+      <c r="C52" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="E52" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="59" t="n"/>
+    </row>
+    <row r="53" outlineLevel="1">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="13" t="n">
+      <c r="C53" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="E53" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="59" t="n"/>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B54" s="59" t="inlineStr">
         <is>
           <t>Essex Fells</t>
         </is>
       </c>
-      <c r="C47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="14" t="n">
+      <c r="C54" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="E54" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="59" t="n"/>
+    </row>
+    <row r="55" outlineLevel="1">
+      <c r="A55" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B55" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C55" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="11" t="n">
+      <c r="D55" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G48" s="13" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="G55" s="59" t="n"/>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B56" s="59" t="inlineStr">
         <is>
           <t>Kearny</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="14" t="n">
+      <c r="C56" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="E56" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="59" t="n"/>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B57" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n">
+      <c r="C57" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="11" t="n">
+      <c r="D57" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G50" s="13" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="G57" s="59" t="n"/>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B58" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C51" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="14" t="n">
+      <c r="C58" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="E58" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="59" t="n"/>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B59" s="59" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="13" t="n">
+      <c r="C59" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="13" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="E59" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="59" t="n"/>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B60" s="59" t="inlineStr">
         <is>
           <t>Short Hills</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="14" t="n">
+      <c r="C60" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="14" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="E60" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="59" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B61" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="13" t="n">
+      <c r="C61" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="13" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="E61" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="59" t="n"/>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B62" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="14" t="n">
+      <c r="C62" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="14" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="E62" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="59" t="n"/>
+    </row>
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="59" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B63" s="59" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="C56" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="13" t="n">
+      <c r="C63" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="11" t="n">
+      <c r="F63" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="13" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="G63" s="59" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="62" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>16 towns</t>
+        </is>
+      </c>
+      <c r="C64" s="63" t="n">
+        <v>32</v>
+      </c>
+      <c r="D64" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" s="63" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="64" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="G64" s="62" t="inlineStr"/>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="57" t="inlineStr">
+        <is>
+          <t>December 2025</t>
+        </is>
+      </c>
+      <c r="B66" s="58" t="n"/>
+      <c r="C66" s="58" t="n"/>
+      <c r="D66" s="58" t="n"/>
+      <c r="E66" s="58" t="n"/>
+      <c r="F66" s="58" t="n"/>
+      <c r="G66" s="58" t="n"/>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B67" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
+      <c r="C67" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D67" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="14" t="n">
+      <c r="E67" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F67" s="61" t="n">
         <v>0.6</v>
       </c>
-      <c r="G57" s="14" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="G67" s="59" t="n"/>
+    </row>
+    <row r="68" outlineLevel="1">
+      <c r="A68" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B68" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C58" s="13" t="n">
+      <c r="C68" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D68" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E68" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="13" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="F68" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="59" t="n"/>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B69" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C59" s="14" t="n">
+      <c r="C69" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="14" t="n">
+      <c r="D69" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="14" t="n">
+      <c r="E69" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F69" s="61" t="n">
         <v>0.4</v>
       </c>
-      <c r="G59" s="14" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="G69" s="59" t="n"/>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B70" s="59" t="inlineStr">
         <is>
           <t>Colonia</t>
         </is>
       </c>
-      <c r="C60" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="13" t="n">
+      <c r="C70" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="E70" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="59" t="n"/>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B71" s="59" t="inlineStr">
         <is>
           <t>Irvington</t>
         </is>
       </c>
-      <c r="C61" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="14" t="n">
+      <c r="C71" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="14" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="E71" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="59" t="n"/>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="A72" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B72" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C62" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="13" t="n">
+      <c r="C72" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="E72" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="59" t="n"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B73" s="59" t="inlineStr">
         <is>
           <t>Lyndhurst</t>
         </is>
       </c>
-      <c r="C63" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="14" t="n">
+      <c r="C73" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="14" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="E73" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="59" t="n"/>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B74" s="59" t="inlineStr">
         <is>
           <t>Pisctaway</t>
         </is>
       </c>
-      <c r="C64" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="13" t="n">
+      <c r="C74" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="E74" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="59" t="n"/>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B75" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C65" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="14" t="n">
+      <c r="C75" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="14" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="E75" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="59" t="n"/>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B76" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C66" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="13" t="n">
+      <c r="C76" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="11" t="n">
+      <c r="F76" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="13" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="G76" s="59" t="n"/>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B77" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C67" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="14" t="n">
+      <c r="C77" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F77" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="14" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="G77" s="59" t="n"/>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B78" s="59" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="C68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="13" t="n">
+      <c r="C78" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="11" t="n">
+      <c r="F78" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G78" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B69" s="14" t="inlineStr">
+      <c r="B79" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C69" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="14" t="n">
+      <c r="C79" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F79" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="14" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="G79" s="59" t="n"/>
+    </row>
+    <row r="80" outlineLevel="1">
+      <c r="A80" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B80" s="59" t="inlineStr">
         <is>
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="C70" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="13" t="n">
+      <c r="C80" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="11" t="n">
+      <c r="F80" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="13" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+      <c r="G80" s="59" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="59" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B81" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C71" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="14" t="n">
+      <c r="C81" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F81" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="14" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="G81" s="59" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="62" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B82" s="62" t="inlineStr">
+        <is>
+          <t>15 towns</t>
+        </is>
+      </c>
+      <c r="C82" s="63" t="n">
+        <v>24</v>
+      </c>
+      <c r="D82" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="F82" s="64" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="G82" s="62" t="inlineStr">
+        <is>
+          <t>1 out of area</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="57" t="inlineStr">
+        <is>
+          <t>January 2026</t>
+        </is>
+      </c>
+      <c r="B84" s="58" t="n"/>
+      <c r="C84" s="58" t="n"/>
+      <c r="D84" s="58" t="n"/>
+      <c r="E84" s="58" t="n"/>
+      <c r="F84" s="58" t="n"/>
+      <c r="G84" s="58" t="n"/>
+    </row>
+    <row r="85" outlineLevel="1">
+      <c r="A85" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B85" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C72" s="13" t="n">
+      <c r="C85" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D72" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="13" t="n">
+      <c r="D85" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="11" t="n">
+      <c r="F85" s="61" t="n">
         <v>0.8</v>
       </c>
-      <c r="G72" s="13" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="G85" s="59" t="n"/>
+    </row>
+    <row r="86" outlineLevel="1">
+      <c r="A86" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B86" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C73" s="14" t="n">
+      <c r="C86" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="14" t="n">
+      <c r="D86" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F86" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G73" s="14" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="G86" s="59" t="n"/>
+    </row>
+    <row r="87" outlineLevel="1">
+      <c r="A87" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B87" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C74" s="13" t="n">
+      <c r="C87" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D87" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E87" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="13" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="F87" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="59" t="n"/>
+    </row>
+    <row r="88" outlineLevel="1">
+      <c r="A88" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B88" s="59" t="inlineStr">
         <is>
           <t>Montville</t>
         </is>
       </c>
-      <c r="C75" s="14" t="n">
+      <c r="C88" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D88" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="14" t="n">
+      <c r="E88" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="14" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="F88" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="59" t="n"/>
+    </row>
+    <row r="89" outlineLevel="1">
+      <c r="A89" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B89" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C76" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="13" t="n">
+      <c r="C89" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="13" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
+      <c r="E89" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="59" t="n"/>
+    </row>
+    <row r="90" outlineLevel="1">
+      <c r="A90" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B90" s="59" t="inlineStr">
         <is>
           <t>East Orange</t>
         </is>
       </c>
-      <c r="C77" s="14" t="n">
+      <c r="C90" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D77" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="6" t="n">
+      <c r="D90" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G77" s="14" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="G90" s="59" t="n"/>
+    </row>
+    <row r="91" outlineLevel="1">
+      <c r="A91" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="B91" s="59" t="inlineStr">
         <is>
           <t>Paterson</t>
         </is>
       </c>
-      <c r="C78" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="13" t="n">
+      <c r="C91" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="13" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="E91" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="59" t="n"/>
+    </row>
+    <row r="92" outlineLevel="1">
+      <c r="A92" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B92" s="59" t="inlineStr">
         <is>
           <t>Waldwick</t>
         </is>
       </c>
-      <c r="C79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="14" t="n">
+      <c r="C92" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="14" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="E92" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="59" t="n"/>
+    </row>
+    <row r="93" outlineLevel="1">
+      <c r="A93" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B93" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="13" t="n">
+      <c r="C93" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="13" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
+      <c r="E93" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="59" t="n"/>
+    </row>
+    <row r="94" outlineLevel="1">
+      <c r="A94" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B94" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C81" s="14" t="n">
+      <c r="C94" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="14" t="n">
+      <c r="D94" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="14" t="n">
+      <c r="E94" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F94" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="14" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="G94" s="59" t="n"/>
+    </row>
+    <row r="95" outlineLevel="1">
+      <c r="A95" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B95" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C82" s="13" t="n">
+      <c r="C95" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D95" s="60" t="n">
         <v>9</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E95" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="11" t="n">
+      <c r="F95" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="13" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="G95" s="59" t="n"/>
+    </row>
+    <row r="96" outlineLevel="1">
+      <c r="A96" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B96" s="59" t="inlineStr">
         <is>
           <t>North Caldwell</t>
         </is>
       </c>
-      <c r="C83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="14" t="n">
+      <c r="C96" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F96" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="14" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="G96" s="59" t="n"/>
+    </row>
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B97" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="13" t="n">
+      <c r="C97" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="11" t="n">
+      <c r="F97" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="13" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr">
+      <c r="G97" s="59" t="n"/>
+    </row>
+    <row r="98" outlineLevel="1">
+      <c r="A98" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B85" s="14" t="inlineStr">
+      <c r="B98" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="14" t="n">
+      <c r="C98" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F98" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="14" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="G98" s="59" t="n"/>
+    </row>
+    <row r="99" outlineLevel="1">
+      <c r="A99" s="59" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="B99" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C86" s="13" t="n">
+      <c r="C99" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="13" t="n">
+      <c r="D99" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="13" t="n">
+      <c r="E99" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="11" t="n">
+      <c r="F99" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="13" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
+      <c r="G99" s="59" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B100" s="62" t="inlineStr">
+        <is>
+          <t>15 towns</t>
+        </is>
+      </c>
+      <c r="C100" s="63" t="n">
+        <v>34</v>
+      </c>
+      <c r="D100" s="63" t="n">
+        <v>19</v>
+      </c>
+      <c r="E100" s="63" t="n">
+        <v>15</v>
+      </c>
+      <c r="F100" s="64" t="n">
+        <v>0.4411764705882353</v>
+      </c>
+      <c r="G100" s="62" t="inlineStr"/>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="57" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="n"/>
+      <c r="C102" s="58" t="n"/>
+      <c r="D102" s="58" t="n"/>
+      <c r="E102" s="58" t="n"/>
+      <c r="F102" s="58" t="n"/>
+      <c r="G102" s="58" t="n"/>
+    </row>
+    <row r="103" outlineLevel="1">
+      <c r="A103" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B87" s="14" t="inlineStr">
+      <c r="B103" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C87" s="14" t="n">
+      <c r="C103" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D87" s="14" t="n">
+      <c r="D103" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E87" s="14" t="n">
+      <c r="E103" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="14" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
+      <c r="F103" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="59" t="n"/>
+    </row>
+    <row r="104" outlineLevel="1">
+      <c r="A104" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B104" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C104" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D88" s="13" t="n">
+      <c r="D104" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E88" s="13" t="n">
+      <c r="E104" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="11" t="n">
+      <c r="F104" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G88" s="13" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="14" t="inlineStr">
+      <c r="G104" s="59" t="n"/>
+    </row>
+    <row r="105" outlineLevel="1">
+      <c r="A105" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B105" s="59" t="inlineStr">
         <is>
           <t>Berkeley Heights</t>
         </is>
       </c>
-      <c r="C89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="14" t="n">
+      <c r="C105" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="14" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+      <c r="E105" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="59" t="n"/>
+    </row>
+    <row r="106" outlineLevel="1">
+      <c r="A106" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B106" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="13" t="n">
+      <c r="C106" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="13" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
+      <c r="E106" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="59" t="n"/>
+    </row>
+    <row r="107" outlineLevel="1">
+      <c r="A107" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B107" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C91" s="14" t="n">
+      <c r="C107" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="6" t="n">
+      <c r="D107" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G91" s="14" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="13" t="inlineStr">
+      <c r="G107" s="59" t="n"/>
+    </row>
+    <row r="108" outlineLevel="1">
+      <c r="A108" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="B108" s="59" t="inlineStr">
         <is>
           <t>Kearny</t>
         </is>
       </c>
-      <c r="C92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="13" t="n">
+      <c r="C108" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="13" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
+      <c r="E108" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="59" t="n"/>
+    </row>
+    <row r="109" outlineLevel="1">
+      <c r="A109" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B93" s="14" t="inlineStr">
+      <c r="B109" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" s="14" t="n">
+      <c r="C109" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="14" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
+      <c r="E109" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="59" t="n"/>
+    </row>
+    <row r="110" outlineLevel="1">
+      <c r="A110" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="B110" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C94" s="13" t="n">
+      <c r="C110" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="11" t="n">
+      <c r="D110" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G94" s="13" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="14" t="inlineStr">
+      <c r="G110" s="59" t="n"/>
+    </row>
+    <row r="111" outlineLevel="1">
+      <c r="A111" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B95" s="14" t="inlineStr">
+      <c r="B111" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="14" t="n">
+      <c r="C111" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="14" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
+      <c r="E111" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="59" t="n"/>
+    </row>
+    <row r="112" outlineLevel="1">
+      <c r="A112" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B112" s="59" t="inlineStr">
         <is>
           <t>Short Hills</t>
         </is>
       </c>
-      <c r="C96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="13" t="n">
+      <c r="C112" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="13" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="E112" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="59" t="n"/>
+    </row>
+    <row r="113" outlineLevel="1">
+      <c r="A113" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B113" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C97" s="14" t="n">
+      <c r="C113" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D97" s="14" t="n">
+      <c r="D113" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="6" t="n">
+      <c r="E113" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="61" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G97" s="14" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
+      <c r="G113" s="59" t="n"/>
+    </row>
+    <row r="114" outlineLevel="1">
+      <c r="A114" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B98" s="13" t="inlineStr">
+      <c r="B114" s="59" t="inlineStr">
         <is>
           <t>Belleville</t>
         </is>
       </c>
-      <c r="C98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="13" t="n">
+      <c r="C114" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F98" s="11" t="n">
+      <c r="F114" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="13" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="G114" s="59" t="n"/>
+    </row>
+    <row r="115" outlineLevel="1">
+      <c r="A115" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B115" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C99" s="14" t="n">
+      <c r="C115" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D99" s="14" t="n">
+      <c r="D115" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E99" s="14" t="n">
+      <c r="E115" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="F115" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="14" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="G115" s="59" t="n"/>
+    </row>
+    <row r="116" outlineLevel="1">
+      <c r="A116" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B116" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C100" s="13" t="n">
+      <c r="C116" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D100" s="13" t="n">
+      <c r="D116" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="13" t="n">
+      <c r="E116" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="11" t="n">
+      <c r="F116" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="13" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="G116" s="59" t="n"/>
+    </row>
+    <row r="117" outlineLevel="1">
+      <c r="A117" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B117" s="59" t="inlineStr">
         <is>
           <t>Essex Fells</t>
         </is>
       </c>
-      <c r="C101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="14" t="n">
+      <c r="C117" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="F117" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="14" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="13" t="inlineStr">
+      <c r="G117" s="59" t="n"/>
+    </row>
+    <row r="118" outlineLevel="1">
+      <c r="A118" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B102" s="13" t="inlineStr">
+      <c r="B118" s="59" t="inlineStr">
         <is>
           <t>Kinnelon</t>
         </is>
       </c>
-      <c r="C102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="13" t="n">
+      <c r="C118" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="11" t="n">
+      <c r="F118" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="13" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="14" t="inlineStr">
+      <c r="G118" s="59" t="n"/>
+    </row>
+    <row r="119" outlineLevel="1">
+      <c r="A119" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B103" s="14" t="inlineStr">
+      <c r="B119" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C103" s="14" t="n">
+      <c r="C119" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D103" s="14" t="n">
+      <c r="D119" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E103" s="14" t="n">
+      <c r="E119" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="F119" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="14" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+      <c r="G119" s="59" t="n"/>
+    </row>
+    <row r="120" outlineLevel="1">
+      <c r="A120" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B120" s="59" t="inlineStr">
         <is>
           <t>Springfield</t>
         </is>
       </c>
-      <c r="C104" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="13" t="n">
+      <c r="C120" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="11" t="n">
+      <c r="F120" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="13" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="14" t="inlineStr">
+      <c r="G120" s="59" t="n"/>
+    </row>
+    <row r="121" outlineLevel="1">
+      <c r="A121" s="59" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B105" s="14" t="inlineStr">
+      <c r="B121" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="14" t="n">
+      <c r="C121" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="F121" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="14" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
+      <c r="G121" s="59" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="62" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B122" s="62" t="inlineStr">
+        <is>
+          <t>19 towns</t>
+        </is>
+      </c>
+      <c r="C122" s="63" t="n">
+        <v>31</v>
+      </c>
+      <c r="D122" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="E122" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="F122" s="64" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="G122" s="62" t="inlineStr"/>
+    </row>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="57" t="inlineStr">
+        <is>
+          <t>March 2026</t>
+        </is>
+      </c>
+      <c r="B124" s="58" t="n"/>
+      <c r="C124" s="58" t="n"/>
+      <c r="D124" s="58" t="n"/>
+      <c r="E124" s="58" t="n"/>
+      <c r="F124" s="58" t="n"/>
+      <c r="G124" s="58" t="n"/>
+    </row>
+    <row r="125" outlineLevel="1">
+      <c r="A125" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="B125" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C106" s="13" t="n">
+      <c r="C125" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D106" s="13" t="n">
+      <c r="D125" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E106" s="13" t="n">
+      <c r="E125" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F106" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="13" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="14" t="inlineStr">
+      <c r="F125" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="59" t="n"/>
+    </row>
+    <row r="126" outlineLevel="1">
+      <c r="A126" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B107" s="14" t="inlineStr">
+      <c r="B126" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C107" s="14" t="n">
+      <c r="C126" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D107" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="14" t="n">
+      <c r="D126" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="F126" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G107" s="14" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="13" t="inlineStr">
+      <c r="G126" s="59" t="n"/>
+    </row>
+    <row r="127" outlineLevel="1">
+      <c r="A127" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B108" s="13" t="inlineStr">
+      <c r="B127" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C108" s="13" t="n">
+      <c r="C127" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D108" s="13" t="n">
+      <c r="D127" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E108" s="13" t="n">
+      <c r="E127" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="11" t="n">
+      <c r="F127" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G108" s="13" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="14" t="inlineStr">
+      <c r="G127" s="59" t="n"/>
+    </row>
+    <row r="128" outlineLevel="1">
+      <c r="A128" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B109" s="14" t="inlineStr">
+      <c r="B128" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C109" s="14" t="n">
+      <c r="C128" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D109" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="14" t="n">
+      <c r="D128" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="F128" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G109" s="14" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="13" t="inlineStr">
+      <c r="G128" s="59" t="n"/>
+    </row>
+    <row r="129" outlineLevel="1">
+      <c r="A129" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B110" s="13" t="inlineStr">
+      <c r="B129" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C110" s="13" t="n">
+      <c r="C129" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D110" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="13" t="n">
+      <c r="D129" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F110" s="11" t="n">
+      <c r="F129" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G110" s="13" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="14" t="inlineStr">
+      <c r="G129" s="59" t="n"/>
+    </row>
+    <row r="130" outlineLevel="1">
+      <c r="A130" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B111" s="14" t="inlineStr">
+      <c r="B130" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C111" s="14" t="n">
+      <c r="C130" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D111" s="14" t="n">
+      <c r="D130" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="14" t="n">
+      <c r="E130" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="6" t="n">
+      <c r="F130" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G111" s="14" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="13" t="inlineStr">
+      <c r="G130" s="59" t="n"/>
+    </row>
+    <row r="131" outlineLevel="1">
+      <c r="A131" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B112" s="13" t="inlineStr">
+      <c r="B131" s="59" t="inlineStr">
         <is>
           <t>(zip in city field)</t>
         </is>
       </c>
-      <c r="C112" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" s="13" t="n">
+      <c r="C131" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="13" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="14" t="inlineStr">
+      <c r="E131" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="59" t="n"/>
+    </row>
+    <row r="132" outlineLevel="1">
+      <c r="A132" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B113" s="14" t="inlineStr">
+      <c r="B132" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C113" s="14" t="n">
+      <c r="C132" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D113" s="14" t="n">
+      <c r="D132" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E113" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="6" t="n">
+      <c r="E132" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="61" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G113" s="14" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
+      <c r="G132" s="59" t="n"/>
+    </row>
+    <row r="133" outlineLevel="1">
+      <c r="A133" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B114" s="13" t="inlineStr">
+      <c r="B133" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C114" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" s="13" t="n">
+      <c r="C133" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="13" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="14" t="inlineStr">
+      <c r="E133" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="59" t="n"/>
+    </row>
+    <row r="134" outlineLevel="1">
+      <c r="A134" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B115" s="14" t="inlineStr">
+      <c r="B134" s="59" t="inlineStr">
         <is>
           <t>Chatham</t>
         </is>
       </c>
-      <c r="C115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D115" s="14" t="n">
+      <c r="C134" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="14" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="13" t="inlineStr">
+      <c r="E134" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="59" t="n"/>
+    </row>
+    <row r="135" outlineLevel="1">
+      <c r="A135" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B116" s="13" t="inlineStr">
+      <c r="B135" s="59" t="inlineStr">
         <is>
           <t>Mountain Lakes</t>
         </is>
       </c>
-      <c r="C116" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" s="13" t="n">
+      <c r="C135" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="13" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="14" t="inlineStr">
+      <c r="E135" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="59" t="n"/>
+    </row>
+    <row r="136" outlineLevel="1">
+      <c r="A136" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B117" s="14" t="inlineStr">
+      <c r="B136" s="59" t="inlineStr">
         <is>
           <t>Wood Ridge</t>
         </is>
       </c>
-      <c r="C117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" s="14" t="n">
+      <c r="C136" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="14" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="13" t="inlineStr">
+      <c r="E136" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="59" t="n"/>
+    </row>
+    <row r="137" outlineLevel="1">
+      <c r="A137" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B118" s="13" t="inlineStr">
+      <c r="B137" s="59" t="inlineStr">
         <is>
           <t>35 Spruce Ct. Clifton</t>
         </is>
       </c>
-      <c r="C118" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="13" t="n">
+      <c r="C137" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="11" t="n">
+      <c r="F137" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="13" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="14" t="inlineStr">
+      <c r="G137" s="59" t="n"/>
+    </row>
+    <row r="138" outlineLevel="1">
+      <c r="A138" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B119" s="14" t="inlineStr">
+      <c r="B138" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C119" s="14" t="n">
+      <c r="C138" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D119" s="14" t="n">
+      <c r="D138" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E119" s="14" t="n">
+      <c r="E138" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="6" t="n">
+      <c r="F138" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="14" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="13" t="inlineStr">
+      <c r="G138" s="59" t="n"/>
+    </row>
+    <row r="139" outlineLevel="1">
+      <c r="A139" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B120" s="13" t="inlineStr">
+      <c r="B139" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C120" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="13" t="n">
+      <c r="C139" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="11" t="n">
+      <c r="F139" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="13" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="14" t="inlineStr">
+      <c r="G139" s="59" t="n"/>
+    </row>
+    <row r="140" outlineLevel="1">
+      <c r="A140" s="59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B121" s="14" t="inlineStr">
+      <c r="B140" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="14" t="n">
+      <c r="C140" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="6" t="n">
+      <c r="F140" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="14" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="13" t="inlineStr">
+      <c r="G140" s="59" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="62" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B141" s="62" t="inlineStr">
+        <is>
+          <t>16 towns</t>
+        </is>
+      </c>
+      <c r="C141" s="63" t="n">
+        <v>33</v>
+      </c>
+      <c r="D141" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="E141" s="63" t="n">
+        <v>19</v>
+      </c>
+      <c r="F141" s="64" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="G141" s="62" t="inlineStr"/>
+    </row>
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" s="57" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="B143" s="58" t="n"/>
+      <c r="C143" s="58" t="n"/>
+      <c r="D143" s="58" t="n"/>
+      <c r="E143" s="58" t="n"/>
+      <c r="F143" s="58" t="n"/>
+      <c r="G143" s="58" t="n"/>
+    </row>
+    <row r="144" outlineLevel="1">
+      <c r="A144" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B122" s="13" t="inlineStr">
+      <c r="B144" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C122" s="13" t="n">
+      <c r="C144" s="60" t="n">
         <v>6</v>
       </c>
-      <c r="D122" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="13" t="n">
+      <c r="D144" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="F122" s="11" t="n">
+      <c r="F144" s="61" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="G122" s="13" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="14" t="inlineStr">
+      <c r="G144" s="59" t="n"/>
+    </row>
+    <row r="145" outlineLevel="1">
+      <c r="A145" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B123" s="14" t="inlineStr">
+      <c r="B145" s="59" t="inlineStr">
         <is>
           <t>East Orange</t>
         </is>
       </c>
-      <c r="C123" s="14" t="n">
+      <c r="C145" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D123" s="14" t="n">
+      <c r="D145" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="14" t="n">
+      <c r="E145" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F123" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="14" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="13" t="inlineStr">
+      <c r="F145" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="59" t="n"/>
+    </row>
+    <row r="146" outlineLevel="1">
+      <c r="A146" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B124" s="13" t="inlineStr">
+      <c r="B146" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C124" s="13" t="n">
+      <c r="C146" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D124" s="13" t="n">
+      <c r="D146" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="13" t="n">
+      <c r="E146" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F124" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="13" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="14" t="inlineStr">
+      <c r="F146" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="59" t="n"/>
+    </row>
+    <row r="147" outlineLevel="1">
+      <c r="A147" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B125" s="14" t="inlineStr">
+      <c r="B147" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C125" s="14" t="n">
+      <c r="C147" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D125" s="14" t="n">
+      <c r="D147" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="14" t="n">
+      <c r="E147" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F125" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="14" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="13" t="inlineStr">
+      <c r="F147" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="59" t="n"/>
+    </row>
+    <row r="148" outlineLevel="1">
+      <c r="A148" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B126" s="13" t="inlineStr">
+      <c r="B148" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C126" s="13" t="n">
+      <c r="C148" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D126" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="13" t="n">
+      <c r="D148" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F126" s="11" t="n">
+      <c r="F148" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G126" s="13" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="14" t="inlineStr">
+      <c r="G148" s="59" t="n"/>
+    </row>
+    <row r="149" outlineLevel="1">
+      <c r="A149" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B127" s="14" t="inlineStr">
+      <c r="B149" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C127" s="14" t="n">
+      <c r="C149" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D127" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="6" t="n">
+      <c r="D149" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G127" s="14" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="13" t="inlineStr">
+      <c r="G149" s="59" t="n"/>
+    </row>
+    <row r="150" outlineLevel="1">
+      <c r="A150" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B128" s="13" t="inlineStr">
+      <c r="B150" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C128" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" s="13" t="n">
+      <c r="C150" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="13" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="14" t="inlineStr">
+      <c r="E150" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="59" t="n"/>
+    </row>
+    <row r="151" outlineLevel="1">
+      <c r="A151" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B151" s="59" t="inlineStr">
         <is>
           <t>East Rutherford</t>
         </is>
       </c>
-      <c r="C129" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" s="14" t="n">
+      <c r="C151" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="14" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="13" t="inlineStr">
+      <c r="E151" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="59" t="n"/>
+    </row>
+    <row r="152" outlineLevel="1">
+      <c r="A152" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B130" s="13" t="inlineStr">
+      <c r="B152" s="59" t="inlineStr">
         <is>
           <t>Edison</t>
         </is>
       </c>
-      <c r="C130" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" s="13" t="n">
+      <c r="C152" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E130" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="13" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
+      <c r="E152" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="59" t="n"/>
+    </row>
+    <row r="153" outlineLevel="1">
+      <c r="A153" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B131" s="14" t="inlineStr">
+      <c r="B153" s="59" t="inlineStr">
         <is>
           <t>Florham Park</t>
         </is>
       </c>
-      <c r="C131" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" s="14" t="n">
+      <c r="C153" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="14" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="13" t="inlineStr">
+      <c r="E153" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="59" t="n"/>
+    </row>
+    <row r="154" outlineLevel="1">
+      <c r="A154" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B132" s="13" t="inlineStr">
+      <c r="B154" s="59" t="inlineStr">
         <is>
           <t>Montville</t>
         </is>
       </c>
-      <c r="C132" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" s="13" t="n">
+      <c r="C154" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="13" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="14" t="inlineStr">
+      <c r="E154" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="59" t="n"/>
+    </row>
+    <row r="155" outlineLevel="1">
+      <c r="A155" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
+      <c r="B155" s="59" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="C133" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D133" s="14" t="n">
+      <c r="C155" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="14" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="13" t="inlineStr">
+      <c r="E155" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="59" t="n"/>
+    </row>
+    <row r="156" outlineLevel="1">
+      <c r="A156" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B134" s="13" t="inlineStr">
+      <c r="B156" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C134" s="13" t="n">
+      <c r="C156" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D134" s="13" t="n">
+      <c r="D156" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E134" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="11" t="n">
+      <c r="E156" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="61" t="n">
         <v>0.25</v>
       </c>
-      <c r="G134" s="13" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="14" t="inlineStr">
+      <c r="G156" s="59" t="n"/>
+    </row>
+    <row r="157" outlineLevel="1">
+      <c r="A157" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B135" s="14" t="inlineStr">
+      <c r="B157" s="59" t="inlineStr">
         <is>
           <t>Denville</t>
         </is>
       </c>
-      <c r="C135" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="14" t="n">
+      <c r="C157" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F135" s="6" t="n">
+      <c r="F157" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G135" s="14" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="13" t="inlineStr">
+      <c r="G157" s="59" t="n"/>
+    </row>
+    <row r="158" outlineLevel="1">
+      <c r="A158" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B136" s="13" t="inlineStr">
+      <c r="B158" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C136" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="13" t="n">
+      <c r="C158" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F136" s="11" t="n">
+      <c r="F158" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G136" s="13" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="14" t="inlineStr">
+      <c r="G158" s="59" t="n"/>
+    </row>
+    <row r="159" outlineLevel="1">
+      <c r="A159" s="59" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr">
+      <c r="B159" s="59" t="inlineStr">
         <is>
           <t>West Caldwell</t>
         </is>
       </c>
-      <c r="C137" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="14" t="n">
+      <c r="C159" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F137" s="6" t="n">
+      <c r="F159" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G137" s="14" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="13" t="inlineStr">
+      <c r="G159" s="59" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="62" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B160" s="62" t="inlineStr">
+        <is>
+          <t>16 towns</t>
+        </is>
+      </c>
+      <c r="C160" s="63" t="n">
+        <v>30</v>
+      </c>
+      <c r="D160" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="E160" s="63" t="n">
+        <v>21</v>
+      </c>
+      <c r="F160" s="64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G160" s="62" t="inlineStr"/>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" s="57" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B162" s="58" t="n"/>
+      <c r="C162" s="58" t="n"/>
+      <c r="D162" s="58" t="n"/>
+      <c r="E162" s="58" t="n"/>
+      <c r="F162" s="58" t="n"/>
+      <c r="G162" s="58" t="n"/>
+    </row>
+    <row r="163" outlineLevel="1">
+      <c r="A163" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B138" s="13" t="inlineStr">
+      <c r="B163" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C138" s="13" t="n">
+      <c r="C163" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D138" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="13" t="n">
+      <c r="D163" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F138" s="11" t="n">
+      <c r="F163" s="61" t="n">
         <v>0.75</v>
       </c>
-      <c r="G138" s="13" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="14" t="inlineStr">
+      <c r="G163" s="59" t="n"/>
+    </row>
+    <row r="164" outlineLevel="1">
+      <c r="A164" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B164" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C139" s="14" t="n">
+      <c r="C164" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D139" s="14" t="n">
+      <c r="D164" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E139" s="14" t="n">
+      <c r="E164" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F139" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="14" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="13" t="inlineStr">
+      <c r="F164" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="59" t="n"/>
+    </row>
+    <row r="165" outlineLevel="1">
+      <c r="A165" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B140" s="13" t="inlineStr">
+      <c r="B165" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C140" s="13" t="n">
+      <c r="C165" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D140" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="13" t="n">
+      <c r="D165" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F140" s="11" t="n">
+      <c r="F165" s="61" t="n">
         <v>0.75</v>
       </c>
-      <c r="G140" s="13" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="14" t="inlineStr">
+      <c r="G165" s="59" t="n"/>
+    </row>
+    <row r="166" outlineLevel="1">
+      <c r="A166" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B141" s="14" t="inlineStr">
+      <c r="B166" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C141" s="14" t="n">
+      <c r="C166" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D141" s="14" t="n">
+      <c r="D166" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E141" s="14" t="n">
+      <c r="E166" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F141" s="6" t="n">
+      <c r="F166" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G141" s="14" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="13" t="inlineStr">
+      <c r="G166" s="59" t="n"/>
+    </row>
+    <row r="167" outlineLevel="1">
+      <c r="A167" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B142" s="13" t="inlineStr">
+      <c r="B167" s="59" t="inlineStr">
         <is>
           <t>Roseland</t>
         </is>
       </c>
-      <c r="C142" s="13" t="n">
+      <c r="C167" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D142" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="13" t="n">
+      <c r="D167" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F142" s="11" t="n">
+      <c r="F167" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G142" s="13" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="14" t="inlineStr">
+      <c r="G167" s="59" t="n"/>
+    </row>
+    <row r="168" outlineLevel="1">
+      <c r="A168" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B143" s="14" t="inlineStr">
+      <c r="B168" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C143" s="14" t="n">
+      <c r="C168" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D143" s="14" t="n">
+      <c r="D168" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="14" t="n">
+      <c r="E168" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F143" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="14" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="13" t="inlineStr">
+      <c r="F168" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="59" t="n"/>
+    </row>
+    <row r="169" outlineLevel="1">
+      <c r="A169" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B144" s="13" t="inlineStr">
+      <c r="B169" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C144" s="13" t="n">
+      <c r="C169" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D144" s="13" t="n">
+      <c r="D169" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E144" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" s="11" t="n">
+      <c r="E169" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="61" t="n">
         <v>0.25</v>
       </c>
-      <c r="G144" s="13" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="14" t="inlineStr">
+      <c r="G169" s="59" t="n"/>
+    </row>
+    <row r="170" outlineLevel="1">
+      <c r="A170" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B145" s="14" t="inlineStr">
+      <c r="B170" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C145" s="14" t="n">
+      <c r="C170" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D145" s="14" t="n">
+      <c r="D170" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E145" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="6" t="n">
+      <c r="E170" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="61" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G145" s="14" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="13" t="inlineStr">
+      <c r="G170" s="59" t="n"/>
+    </row>
+    <row r="171" outlineLevel="1">
+      <c r="A171" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B146" s="13" t="inlineStr">
+      <c r="B171" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C146" s="13" t="n">
+      <c r="C171" s="60" t="n">
         <v>6</v>
       </c>
-      <c r="D146" s="13" t="n">
+      <c r="D171" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="E146" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" s="11" t="n">
+      <c r="E171" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="61" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="G146" s="13" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="14" t="inlineStr">
+      <c r="G171" s="59" t="n"/>
+    </row>
+    <row r="172" outlineLevel="1">
+      <c r="A172" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B147" s="14" t="inlineStr">
+      <c r="B172" s="59" t="inlineStr">
         <is>
           <t>Newark</t>
         </is>
       </c>
-      <c r="C147" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" s="14" t="n">
+      <c r="C172" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E147" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="14" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="13" t="inlineStr">
+      <c r="E172" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="59" t="n"/>
+    </row>
+    <row r="173" outlineLevel="1">
+      <c r="A173" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B148" s="13" t="inlineStr">
+      <c r="B173" s="59" t="inlineStr">
         <is>
           <t>Wayne</t>
         </is>
       </c>
-      <c r="C148" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D148" s="13" t="n">
+      <c r="C173" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E148" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="13" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="14" t="inlineStr">
+      <c r="E173" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="59" t="n"/>
+    </row>
+    <row r="174" outlineLevel="1">
+      <c r="A174" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B149" s="14" t="inlineStr">
+      <c r="B174" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C149" s="14" t="n">
+      <c r="C174" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D149" s="14" t="n">
+      <c r="D174" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E149" s="14" t="n">
+      <c r="E174" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F149" s="6" t="n">
+      <c r="F174" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G149" s="14" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="13" t="inlineStr">
+      <c r="G174" s="59" t="n"/>
+    </row>
+    <row r="175" outlineLevel="1">
+      <c r="A175" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B150" s="13" t="inlineStr">
+      <c r="B175" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C150" s="13" t="n">
+      <c r="C175" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D150" s="13" t="n">
+      <c r="D175" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E150" s="13" t="n">
+      <c r="E175" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F150" s="11" t="n">
+      <c r="F175" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G150" s="13" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="14" t="inlineStr">
+      <c r="G175" s="59" t="n"/>
+    </row>
+    <row r="176" outlineLevel="1">
+      <c r="A176" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B151" s="14" t="inlineStr">
+      <c r="B176" s="59" t="inlineStr">
         <is>
           <t>Chatham Township</t>
         </is>
       </c>
-      <c r="C151" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="14" t="n">
+      <c r="C176" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F151" s="6" t="n">
+      <c r="F176" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="14" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="13" t="inlineStr">
+      <c r="G176" s="59" t="n"/>
+    </row>
+    <row r="177" outlineLevel="1">
+      <c r="A177" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B152" s="13" t="inlineStr">
+      <c r="B177" s="59" t="inlineStr">
         <is>
           <t>Little Falls</t>
         </is>
       </c>
-      <c r="C152" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="13" t="n">
+      <c r="C177" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F152" s="11" t="n">
+      <c r="F177" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G152" s="13" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="14" t="inlineStr">
+      <c r="G177" s="59" t="n"/>
+    </row>
+    <row r="178" outlineLevel="1">
+      <c r="A178" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B153" s="14" t="inlineStr">
+      <c r="B178" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C153" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" s="14" t="n">
+      <c r="C178" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F153" s="6" t="n">
+      <c r="F178" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G153" s="14" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="13" t="inlineStr">
+      <c r="G178" s="59" t="n"/>
+    </row>
+    <row r="179" outlineLevel="1">
+      <c r="A179" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B154" s="13" t="inlineStr">
+      <c r="B179" s="59" t="inlineStr">
         <is>
           <t>Paterson</t>
         </is>
       </c>
-      <c r="C154" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" s="13" t="n">
+      <c r="C179" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F154" s="11" t="n">
+      <c r="F179" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G154" s="13" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="14" t="inlineStr">
+      <c r="G179" s="59" t="n"/>
+    </row>
+    <row r="180" outlineLevel="1">
+      <c r="A180" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B155" s="14" t="inlineStr">
+      <c r="B180" s="59" t="inlineStr">
         <is>
           <t>Vauxhall</t>
         </is>
       </c>
-      <c r="C155" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" s="14" t="n">
+      <c r="C180" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F155" s="6" t="n">
+      <c r="F180" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G155" s="14" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="13" t="inlineStr">
+      <c r="G180" s="59" t="n"/>
+    </row>
+    <row r="181" outlineLevel="1">
+      <c r="A181" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B156" s="13" t="inlineStr">
+      <c r="B181" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C156" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D156" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="13" t="n">
+      <c r="C181" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="11" t="n">
+      <c r="F181" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G156" s="13" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="14" t="inlineStr">
+      <c r="G181" s="59" t="n"/>
+    </row>
+    <row r="182" outlineLevel="1">
+      <c r="A182" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B157" s="14" t="inlineStr">
+      <c r="B182" s="59" t="inlineStr">
         <is>
           <t>West Caldwell</t>
         </is>
       </c>
-      <c r="C157" s="14" t="n">
+      <c r="C182" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D157" s="14" t="n">
+      <c r="D182" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E157" s="14" t="n">
+      <c r="E182" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F157" s="6" t="n">
+      <c r="F182" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G157" s="14" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="13" t="inlineStr">
+      <c r="G182" s="59" t="n"/>
+    </row>
+    <row r="183" outlineLevel="1">
+      <c r="A183" s="59" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B158" s="13" t="inlineStr">
+      <c r="B183" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C158" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D158" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="13" t="n">
+      <c r="C183" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F158" s="11" t="n">
+      <c r="F183" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G158" s="13" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="14" t="inlineStr">
+      <c r="G183" s="59" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="62" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B184" s="62" t="inlineStr">
+        <is>
+          <t>21 towns</t>
+        </is>
+      </c>
+      <c r="C184" s="63" t="n">
+        <v>49</v>
+      </c>
+      <c r="D184" s="63" t="n">
+        <v>29</v>
+      </c>
+      <c r="E184" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F184" s="64" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="G184" s="62" t="inlineStr"/>
+    </row>
+    <row r="185"/>
+    <row r="186">
+      <c r="A186" s="57" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="B186" s="58" t="n"/>
+      <c r="C186" s="58" t="n"/>
+      <c r="D186" s="58" t="n"/>
+      <c r="E186" s="58" t="n"/>
+      <c r="F186" s="58" t="n"/>
+      <c r="G186" s="58" t="n"/>
+    </row>
+    <row r="187" outlineLevel="1">
+      <c r="A187" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B159" s="14" t="inlineStr">
+      <c r="B187" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C159" s="14" t="n">
+      <c r="C187" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D159" s="14" t="n">
+      <c r="D187" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E159" s="14" t="n">
+      <c r="E187" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F159" s="6" t="n">
+      <c r="F187" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G159" s="14" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="13" t="inlineStr">
+      <c r="G187" s="59" t="n"/>
+    </row>
+    <row r="188" outlineLevel="1">
+      <c r="A188" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B160" s="13" t="inlineStr">
+      <c r="B188" s="59" t="inlineStr">
         <is>
           <t>Hillside</t>
         </is>
       </c>
-      <c r="C160" s="13" t="n">
+      <c r="C188" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D160" s="13" t="n">
+      <c r="D188" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E160" s="13" t="n">
+      <c r="E188" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F160" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" s="13" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="14" t="inlineStr">
+      <c r="F188" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="59" t="n"/>
+    </row>
+    <row r="189" outlineLevel="1">
+      <c r="A189" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B161" s="14" t="inlineStr">
+      <c r="B189" s="59" t="inlineStr">
         <is>
           <t>Secaucus</t>
         </is>
       </c>
-      <c r="C161" s="14" t="n">
+      <c r="C189" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D161" s="14" t="n">
+      <c r="D189" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E161" s="14" t="n">
+      <c r="E189" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F161" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" s="14" t="inlineStr">
+      <c r="F189" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="13" t="inlineStr">
+    <row r="190" outlineLevel="1">
+      <c r="A190" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B162" s="13" t="inlineStr">
+      <c r="B190" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C162" s="13" t="n">
+      <c r="C190" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="n">
+      <c r="D190" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E162" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" s="11" t="n">
+      <c r="E190" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="61" t="n">
         <v>0.25</v>
       </c>
-      <c r="G162" s="13" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="14" t="inlineStr">
+      <c r="G190" s="59" t="n"/>
+    </row>
+    <row r="191" outlineLevel="1">
+      <c r="A191" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B163" s="14" t="inlineStr">
+      <c r="B191" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C163" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" s="14" t="n">
+      <c r="C191" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E163" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" s="14" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="13" t="inlineStr">
+      <c r="E191" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="59" t="n"/>
+    </row>
+    <row r="192" outlineLevel="1">
+      <c r="A192" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B164" s="13" t="inlineStr">
+      <c r="B192" s="59" t="inlineStr">
         <is>
           <t>East Orange</t>
         </is>
       </c>
-      <c r="C164" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" s="13" t="n">
+      <c r="C192" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E164" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="13" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="14" t="inlineStr">
+      <c r="E192" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="59" t="n"/>
+    </row>
+    <row r="193" outlineLevel="1">
+      <c r="A193" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B165" s="14" t="inlineStr">
+      <c r="B193" s="59" t="inlineStr">
         <is>
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="C165" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" s="14" t="n">
+      <c r="C193" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E165" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" s="14" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="13" t="inlineStr">
+      <c r="E193" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="59" t="n"/>
+    </row>
+    <row r="194" outlineLevel="1">
+      <c r="A194" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B166" s="13" t="inlineStr">
+      <c r="B194" s="59" t="inlineStr">
         <is>
           <t>Hewitt</t>
         </is>
       </c>
-      <c r="C166" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" s="13" t="n">
+      <c r="C194" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E166" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" s="13" t="inlineStr">
+      <c r="E194" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="14" t="inlineStr">
+    <row r="195" outlineLevel="1">
+      <c r="A195" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B167" s="14" t="inlineStr">
+      <c r="B195" s="59" t="inlineStr">
         <is>
           <t>Jersey City</t>
         </is>
       </c>
-      <c r="C167" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" s="14" t="n">
+      <c r="C195" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E167" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G167" s="14" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="13" t="inlineStr">
+      <c r="E195" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="59" t="n"/>
+    </row>
+    <row r="196" outlineLevel="1">
+      <c r="A196" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B168" s="13" t="inlineStr">
+      <c r="B196" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C168" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" s="13" t="n">
+      <c r="C196" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E168" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" s="13" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="14" t="inlineStr">
+      <c r="E196" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="59" t="n"/>
+    </row>
+    <row r="197" outlineLevel="1">
+      <c r="A197" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B169" s="14" t="inlineStr">
+      <c r="B197" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C169" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" s="14" t="n">
+      <c r="C197" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E169" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="14" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="13" t="inlineStr">
+      <c r="E197" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="59" t="n"/>
+    </row>
+    <row r="198" outlineLevel="1">
+      <c r="A198" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B170" s="13" t="inlineStr">
+      <c r="B198" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C170" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D170" s="13" t="n">
+      <c r="C198" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E170" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" s="13" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="14" t="inlineStr">
+      <c r="E198" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="59" t="n"/>
+    </row>
+    <row r="199" outlineLevel="1">
+      <c r="A199" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B171" s="14" t="inlineStr">
+      <c r="B199" s="59" t="inlineStr">
         <is>
           <t>Nanuet</t>
         </is>
       </c>
-      <c r="C171" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D171" s="14" t="n">
+      <c r="C199" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E171" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" s="14" t="inlineStr">
+      <c r="E199" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="13" t="inlineStr">
+    <row r="200" outlineLevel="1">
+      <c r="A200" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B172" s="13" t="inlineStr">
+      <c r="B200" s="59" t="inlineStr">
         <is>
           <t>Pompton Plains</t>
         </is>
       </c>
-      <c r="C172" s="13" t="n">
+      <c r="C200" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D172" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" s="11" t="n">
+      <c r="D200" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G172" s="13" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="14" t="inlineStr">
+      <c r="G200" s="59" t="n"/>
+    </row>
+    <row r="201" outlineLevel="1">
+      <c r="A201" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B173" s="14" t="inlineStr">
+      <c r="B201" s="59" t="inlineStr">
         <is>
           <t>Roseland</t>
         </is>
       </c>
-      <c r="C173" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D173" s="14" t="n">
+      <c r="C201" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E173" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" s="14" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="13" t="inlineStr">
+      <c r="E201" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="59" t="n"/>
+    </row>
+    <row r="202" outlineLevel="1">
+      <c r="A202" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B174" s="13" t="inlineStr">
+      <c r="B202" s="59" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="C174" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D174" s="13" t="n">
+      <c r="C202" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" s="13" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="14" t="inlineStr">
+      <c r="E202" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="59" t="n"/>
+    </row>
+    <row r="203" outlineLevel="1">
+      <c r="A203" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B175" s="14" t="inlineStr">
+      <c r="B203" s="59" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="C175" s="14" t="n">
+      <c r="C203" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D175" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" s="6" t="n">
+      <c r="D203" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G175" s="14" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="13" t="inlineStr">
+      <c r="G203" s="59" t="n"/>
+    </row>
+    <row r="204" outlineLevel="1">
+      <c r="A204" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B176" s="13" t="inlineStr">
+      <c r="B204" s="59" t="inlineStr">
         <is>
           <t>Wayne</t>
         </is>
       </c>
-      <c r="C176" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" s="13" t="n">
+      <c r="C204" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E176" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" s="13" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="14" t="inlineStr">
+      <c r="E204" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="59" t="n"/>
+    </row>
+    <row r="205" outlineLevel="1">
+      <c r="A205" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B177" s="14" t="inlineStr">
+      <c r="B205" s="59" t="inlineStr">
         <is>
           <t>(zip in city field)</t>
         </is>
       </c>
-      <c r="C177" s="14" t="n">
+      <c r="C205" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D177" s="14" t="n">
+      <c r="D205" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E177" s="14" t="n">
+      <c r="E205" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F177" s="6" t="n">
+      <c r="F205" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G177" s="14" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="13" t="inlineStr">
+      <c r="G205" s="59" t="n"/>
+    </row>
+    <row r="206" outlineLevel="1">
+      <c r="A206" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B178" s="13" t="inlineStr">
+      <c r="B206" s="59" t="inlineStr">
         <is>
           <t>Denville</t>
         </is>
       </c>
-      <c r="C178" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D178" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="13" t="n">
+      <c r="C206" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F178" s="11" t="n">
+      <c r="F206" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G178" s="13" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="14" t="inlineStr">
+      <c r="G206" s="59" t="n"/>
+    </row>
+    <row r="207" outlineLevel="1">
+      <c r="A207" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B179" s="14" t="inlineStr">
+      <c r="B207" s="59" t="inlineStr">
         <is>
           <t>Passaic</t>
         </is>
       </c>
-      <c r="C179" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" s="14" t="n">
+      <c r="C207" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F179" s="6" t="n">
+      <c r="F207" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G179" s="14" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="13" t="inlineStr">
+      <c r="G207" s="59" t="n"/>
+    </row>
+    <row r="208" outlineLevel="1">
+      <c r="A208" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B180" s="13" t="inlineStr">
+      <c r="B208" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C180" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="13" t="n">
+      <c r="C208" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F180" s="11" t="n">
+      <c r="F208" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G180" s="13" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="14" t="inlineStr">
+      <c r="G208" s="59" t="n"/>
+    </row>
+    <row r="209" outlineLevel="1">
+      <c r="A209" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B181" s="14" t="inlineStr">
+      <c r="B209" s="59" t="inlineStr">
         <is>
           <t>West Caldwell</t>
         </is>
       </c>
-      <c r="C181" s="14" t="n">
+      <c r="C209" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D181" s="14" t="n">
+      <c r="D209" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="14" t="n">
+      <c r="E209" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F181" s="6" t="n">
+      <c r="F209" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G181" s="14" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="13" t="inlineStr">
+      <c r="G209" s="59" t="n"/>
+    </row>
+    <row r="210" outlineLevel="1">
+      <c r="A210" s="59" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B182" s="13" t="inlineStr">
+      <c r="B210" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C182" s="13" t="n">
+      <c r="C210" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D182" s="13" t="n">
+      <c r="D210" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="E182" s="13" t="n">
+      <c r="E210" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F182" s="11" t="n">
+      <c r="F210" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G182" s="13" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="14" t="inlineStr">
+      <c r="G210" s="59" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="62" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B211" s="62" t="inlineStr">
+        <is>
+          <t>24 towns</t>
+        </is>
+      </c>
+      <c r="C211" s="63" t="n">
+        <v>39</v>
+      </c>
+      <c r="D211" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="E211" s="63" t="n">
+        <v>21</v>
+      </c>
+      <c r="F211" s="64" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G211" s="62" t="inlineStr">
+        <is>
+          <t>3 out of area</t>
+        </is>
+      </c>
+    </row>
+    <row r="212"/>
+    <row r="213">
+      <c r="A213" s="57" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="B213" s="58" t="n"/>
+      <c r="C213" s="58" t="n"/>
+      <c r="D213" s="58" t="n"/>
+      <c r="E213" s="58" t="n"/>
+      <c r="F213" s="58" t="n"/>
+      <c r="G213" s="58" t="n"/>
+    </row>
+    <row r="214" outlineLevel="1">
+      <c r="A214" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B183" s="14" t="inlineStr">
+      <c r="B214" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C183" s="14" t="n">
+      <c r="C214" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D183" s="14" t="n">
+      <c r="D214" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E183" s="14" t="n">
+      <c r="E214" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F183" s="6" t="n">
+      <c r="F214" s="61" t="n">
         <v>0.6</v>
       </c>
-      <c r="G183" s="14" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="13" t="inlineStr">
+      <c r="G214" s="59" t="n"/>
+    </row>
+    <row r="215" outlineLevel="1">
+      <c r="A215" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B184" s="13" t="inlineStr">
+      <c r="B215" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C184" s="13" t="n">
+      <c r="C215" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D184" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" s="13" t="n">
+      <c r="D215" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F184" s="11" t="n">
+      <c r="F215" s="61" t="n">
         <v>0.75</v>
       </c>
-      <c r="G184" s="13" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="14" t="inlineStr">
+      <c r="G215" s="59" t="n"/>
+    </row>
+    <row r="216" outlineLevel="1">
+      <c r="A216" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B185" s="14" t="inlineStr">
+      <c r="B216" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C185" s="14" t="n">
+      <c r="C216" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D185" s="14" t="n">
+      <c r="D216" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E185" s="14" t="n">
+      <c r="E216" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F185" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="14" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="13" t="inlineStr">
+      <c r="F216" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="59" t="n"/>
+    </row>
+    <row r="217" outlineLevel="1">
+      <c r="A217" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B186" s="13" t="inlineStr">
+      <c r="B217" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C186" s="13" t="n">
+      <c r="C217" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D186" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" s="13" t="n">
+      <c r="D217" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F186" s="11" t="n">
+      <c r="F217" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G186" s="13" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="14" t="inlineStr">
+      <c r="G217" s="59" t="n"/>
+    </row>
+    <row r="218" outlineLevel="1">
+      <c r="A218" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B187" s="14" t="inlineStr">
+      <c r="B218" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C187" s="14" t="n">
+      <c r="C218" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="D187" s="14" t="n">
+      <c r="D218" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E187" s="14" t="n">
+      <c r="E218" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F187" s="6" t="n">
+      <c r="F218" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G187" s="14" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="13" t="inlineStr">
+      <c r="G218" s="59" t="n"/>
+    </row>
+    <row r="219" outlineLevel="1">
+      <c r="A219" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B188" s="13" t="inlineStr">
+      <c r="B219" s="59" t="inlineStr">
         <is>
           <t>Dover</t>
         </is>
       </c>
-      <c r="C188" s="13" t="n">
+      <c r="C219" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D188" s="13" t="n">
+      <c r="D219" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E188" s="13" t="n">
+      <c r="E219" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F188" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" s="13" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="14" t="inlineStr">
+      <c r="F219" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="59" t="n"/>
+    </row>
+    <row r="220" outlineLevel="1">
+      <c r="A220" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B189" s="14" t="inlineStr">
+      <c r="B220" s="59" t="inlineStr">
         <is>
           <t>Essex Fells</t>
         </is>
       </c>
-      <c r="C189" s="14" t="n">
+      <c r="C220" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D189" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E189" s="14" t="n">
+      <c r="D220" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F189" s="6" t="n">
+      <c r="F220" s="61" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G189" s="14" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="13" t="inlineStr">
+      <c r="G220" s="59" t="n"/>
+    </row>
+    <row r="221" outlineLevel="1">
+      <c r="A221" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B190" s="13" t="inlineStr">
+      <c r="B221" s="59" t="inlineStr">
         <is>
           <t>Montville</t>
         </is>
       </c>
-      <c r="C190" s="13" t="n">
+      <c r="C221" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D190" s="13" t="n">
+      <c r="D221" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E190" s="13" t="n">
+      <c r="E221" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F190" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" s="13" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="14" t="inlineStr">
+      <c r="F221" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="59" t="n"/>
+    </row>
+    <row r="222" outlineLevel="1">
+      <c r="A222" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B191" s="14" t="inlineStr">
+      <c r="B222" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C191" s="14" t="n">
+      <c r="C222" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D191" s="14" t="n">
+      <c r="D222" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E191" s="14" t="n">
+      <c r="E222" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F191" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" s="14" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="13" t="inlineStr">
+      <c r="F222" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="59" t="n"/>
+    </row>
+    <row r="223" outlineLevel="1">
+      <c r="A223" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B192" s="13" t="inlineStr">
+      <c r="B223" s="59" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="C192" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D192" s="13" t="n">
+      <c r="C223" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E192" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" s="13" t="inlineStr">
+      <c r="E223" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="14" t="inlineStr">
+    <row r="224" outlineLevel="1">
+      <c r="A224" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B193" s="14" t="inlineStr">
+      <c r="B224" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C193" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D193" s="14" t="n">
+      <c r="C224" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F193" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" s="14" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="13" t="inlineStr">
+      <c r="E224" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="59" t="n"/>
+    </row>
+    <row r="225" outlineLevel="1">
+      <c r="A225" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B194" s="13" t="inlineStr">
+      <c r="B225" s="59" t="inlineStr">
         <is>
           <t>East Orange</t>
         </is>
       </c>
-      <c r="C194" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D194" s="13" t="n">
+      <c r="C225" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E194" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" s="13" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="14" t="inlineStr">
+      <c r="E225" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="59" t="n"/>
+    </row>
+    <row r="226" outlineLevel="1">
+      <c r="A226" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B195" s="14" t="inlineStr">
+      <c r="B226" s="59" t="inlineStr">
         <is>
           <t>Freehold</t>
         </is>
       </c>
-      <c r="C195" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D195" s="14" t="n">
+      <c r="C226" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E195" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" s="14" t="inlineStr">
+      <c r="E226" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="13" t="inlineStr">
+    <row r="227" outlineLevel="1">
+      <c r="A227" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B196" s="13" t="inlineStr">
+      <c r="B227" s="59" t="inlineStr">
         <is>
           <t>Lake Hiawatha</t>
         </is>
       </c>
-      <c r="C196" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D196" s="13" t="n">
+      <c r="C227" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E196" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" s="13" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="14" t="inlineStr">
+      <c r="E227" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="59" t="n"/>
+    </row>
+    <row r="228" outlineLevel="1">
+      <c r="A228" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B197" s="14" t="inlineStr">
+      <c r="B228" s="59" t="inlineStr">
         <is>
           <t>North Bergen</t>
         </is>
       </c>
-      <c r="C197" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D197" s="14" t="n">
+      <c r="C228" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E197" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="14" t="inlineStr">
+      <c r="E228" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="13" t="inlineStr">
+    <row r="229" outlineLevel="1">
+      <c r="A229" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B198" s="13" t="inlineStr">
+      <c r="B229" s="59" t="inlineStr">
         <is>
           <t>Roseland</t>
         </is>
       </c>
-      <c r="C198" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D198" s="13" t="n">
+      <c r="C229" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E198" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="13" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="14" t="inlineStr">
+      <c r="E229" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="59" t="n"/>
+    </row>
+    <row r="230" outlineLevel="1">
+      <c r="A230" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B199" s="14" t="inlineStr">
+      <c r="B230" s="59" t="inlineStr">
         <is>
           <t>Totowa</t>
         </is>
       </c>
-      <c r="C199" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D199" s="14" t="n">
+      <c r="C230" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E199" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="14" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="13" t="inlineStr">
+      <c r="E230" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="59" t="n"/>
+    </row>
+    <row r="231" outlineLevel="1">
+      <c r="A231" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B200" s="13" t="inlineStr">
+      <c r="B231" s="59" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="C200" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D200" s="13" t="n">
+      <c r="C231" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="13" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="14" t="inlineStr">
+      <c r="E231" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="59" t="n"/>
+    </row>
+    <row r="232" outlineLevel="1">
+      <c r="A232" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B201" s="14" t="inlineStr">
+      <c r="B232" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C201" s="14" t="n">
+      <c r="C232" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D201" s="14" t="n">
+      <c r="D232" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E201" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" s="6" t="n">
+      <c r="E232" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="61" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G201" s="14" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="13" t="inlineStr">
+      <c r="G232" s="59" t="n"/>
+    </row>
+    <row r="233" outlineLevel="1">
+      <c r="A233" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B202" s="13" t="inlineStr">
+      <c r="B233" s="59" t="inlineStr">
         <is>
           <t>Fairfield</t>
         </is>
       </c>
-      <c r="C202" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D202" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" s="13" t="n">
+      <c r="C233" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F202" s="11" t="n">
+      <c r="F233" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G202" s="13" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="14" t="inlineStr">
+      <c r="G233" s="59" t="n"/>
+    </row>
+    <row r="234" outlineLevel="1">
+      <c r="A234" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B203" s="14" t="inlineStr">
+      <c r="B234" s="59" t="inlineStr">
         <is>
           <t>Glen Ridge</t>
         </is>
       </c>
-      <c r="C203" s="14" t="n">
+      <c r="C234" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D203" s="14" t="n">
+      <c r="D234" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E203" s="14" t="n">
+      <c r="E234" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F203" s="6" t="n">
+      <c r="F234" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G203" s="14" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="13" t="inlineStr">
+      <c r="G234" s="59" t="n"/>
+    </row>
+    <row r="235" outlineLevel="1">
+      <c r="A235" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B204" s="13" t="inlineStr">
+      <c r="B235" s="59" t="inlineStr">
         <is>
           <t>Little Falls</t>
         </is>
       </c>
-      <c r="C204" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D204" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E204" s="13" t="n">
+      <c r="C235" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F204" s="11" t="n">
+      <c r="F235" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G204" s="13" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="14" t="inlineStr">
+      <c r="G235" s="59" t="n"/>
+    </row>
+    <row r="236" outlineLevel="1">
+      <c r="A236" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B205" s="14" t="inlineStr">
+      <c r="B236" s="59" t="inlineStr">
         <is>
           <t>Livingston</t>
         </is>
       </c>
-      <c r="C205" s="14" t="n">
+      <c r="C236" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D205" s="14" t="n">
+      <c r="D236" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E205" s="14" t="n">
+      <c r="E236" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F205" s="6" t="n">
+      <c r="F236" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G205" s="14" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="13" t="inlineStr">
+      <c r="G236" s="59" t="n"/>
+    </row>
+    <row r="237" outlineLevel="1">
+      <c r="A237" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B206" s="13" t="inlineStr">
+      <c r="B237" s="59" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="C206" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D206" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" s="13" t="n">
+      <c r="C237" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F206" s="11" t="n">
+      <c r="F237" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G206" s="13" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="14" t="inlineStr">
+      <c r="G237" s="59" t="n"/>
+    </row>
+    <row r="238" outlineLevel="1">
+      <c r="A238" s="59" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B207" s="14" t="inlineStr">
+      <c r="B238" s="59" t="inlineStr">
         <is>
           <t>Woodland Park</t>
         </is>
       </c>
-      <c r="C207" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D207" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E207" s="14" t="n">
+      <c r="C238" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F207" s="6" t="n">
+      <c r="F238" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G207" s="14" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="13" t="inlineStr">
+      <c r="G238" s="59" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="62" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B239" s="62" t="inlineStr">
+        <is>
+          <t>25 towns</t>
+        </is>
+      </c>
+      <c r="C239" s="63" t="n">
+        <v>48</v>
+      </c>
+      <c r="D239" s="63" t="n">
+        <v>17</v>
+      </c>
+      <c r="E239" s="63" t="n">
+        <v>31</v>
+      </c>
+      <c r="F239" s="64" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G239" s="62" t="inlineStr">
+        <is>
+          <t>3 out of area</t>
+        </is>
+      </c>
+    </row>
+    <row r="240"/>
+    <row r="241">
+      <c r="A241" s="57" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B241" s="58" t="n"/>
+      <c r="C241" s="58" t="n"/>
+      <c r="D241" s="58" t="n"/>
+      <c r="E241" s="58" t="n"/>
+      <c r="F241" s="58" t="n"/>
+      <c r="G241" s="58" t="n"/>
+    </row>
+    <row r="242" outlineLevel="1">
+      <c r="A242" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B208" s="13" t="inlineStr">
+      <c r="B242" s="59" t="inlineStr">
         <is>
           <t>West Orange</t>
         </is>
       </c>
-      <c r="C208" s="13" t="n">
+      <c r="C242" s="60" t="n">
         <v>7</v>
       </c>
-      <c r="D208" s="13" t="n">
+      <c r="D242" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E208" s="13" t="n">
+      <c r="E242" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="F208" s="11" t="n">
+      <c r="F242" s="61" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="G208" s="13" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="14" t="inlineStr">
+      <c r="G242" s="59" t="n"/>
+    </row>
+    <row r="243" outlineLevel="1">
+      <c r="A243" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B209" s="14" t="inlineStr">
+      <c r="B243" s="59" t="inlineStr">
         <is>
           <t>Bloomfield</t>
         </is>
       </c>
-      <c r="C209" s="14" t="n">
+      <c r="C243" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D209" s="14" t="n">
+      <c r="D243" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="14" t="n">
+      <c r="E243" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F209" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="14" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="13" t="inlineStr">
+      <c r="F243" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" s="59" t="n"/>
+    </row>
+    <row r="244" outlineLevel="1">
+      <c r="A244" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B210" s="13" t="inlineStr">
+      <c r="B244" s="59" t="inlineStr">
         <is>
           <t>Clifton</t>
         </is>
       </c>
-      <c r="C210" s="13" t="n">
+      <c r="C244" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D210" s="13" t="n">
+      <c r="D244" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="13" t="n">
+      <c r="E244" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F210" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" s="13" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="14" t="inlineStr">
+      <c r="F244" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" s="59" t="n"/>
+    </row>
+    <row r="245" outlineLevel="1">
+      <c r="A245" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B211" s="14" t="inlineStr">
+      <c r="B245" s="59" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="C211" s="14" t="n">
+      <c r="C245" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D211" s="14" t="n">
+      <c r="D245" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E211" s="14" t="n">
+      <c r="E245" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F211" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="14" t="inlineStr">
+      <c r="F245" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="13" t="inlineStr">
+    <row r="246" outlineLevel="1">
+      <c r="A246" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B212" s="13" t="inlineStr">
+      <c r="B246" s="59" t="inlineStr">
         <is>
           <t>Nutley</t>
         </is>
       </c>
-      <c r="C212" s="13" t="n">
+      <c r="C246" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D212" s="13" t="n">
+      <c r="D246" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="13" t="n">
+      <c r="E246" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F212" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" s="13" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="14" t="inlineStr">
+      <c r="F246" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="59" t="n"/>
+    </row>
+    <row r="247" outlineLevel="1">
+      <c r="A247" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B213" s="14" t="inlineStr">
+      <c r="B247" s="59" t="inlineStr">
         <is>
           <t>South Orange</t>
         </is>
       </c>
-      <c r="C213" s="14" t="n">
+      <c r="C247" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D213" s="14" t="n">
+      <c r="D247" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E213" s="14" t="n">
+      <c r="E247" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="F213" s="6" t="n">
+      <c r="F247" s="61" t="n">
         <v>0.4</v>
       </c>
-      <c r="G213" s="14" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="13" t="inlineStr">
+      <c r="G247" s="59" t="n"/>
+    </row>
+    <row r="248" outlineLevel="1">
+      <c r="A248" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B214" s="13" t="inlineStr">
+      <c r="B248" s="59" t="inlineStr">
         <is>
           <t>Bayonne</t>
         </is>
       </c>
-      <c r="C214" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D214" s="13" t="n">
+      <c r="C248" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F214" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" s="13" t="inlineStr">
+      <c r="E248" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="14" t="inlineStr">
+    <row r="249" outlineLevel="1">
+      <c r="A249" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B215" s="14" t="inlineStr">
+      <c r="B249" s="59" t="inlineStr">
         <is>
           <t>Caldwell</t>
         </is>
       </c>
-      <c r="C215" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D215" s="14" t="n">
+      <c r="C249" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F215" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" s="14" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="13" t="inlineStr">
+      <c r="E249" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="59" t="n"/>
+    </row>
+    <row r="250" outlineLevel="1">
+      <c r="A250" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B216" s="13" t="inlineStr">
+      <c r="B250" s="59" t="inlineStr">
         <is>
           <t>Cedar Grove</t>
         </is>
       </c>
-      <c r="C216" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D216" s="13" t="n">
+      <c r="C250" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F216" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" s="13" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="14" t="inlineStr">
+      <c r="E250" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" s="59" t="n"/>
+    </row>
+    <row r="251" outlineLevel="1">
+      <c r="A251" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B217" s="14" t="inlineStr">
+      <c r="B251" s="59" t="inlineStr">
         <is>
           <t>Chatham</t>
         </is>
       </c>
-      <c r="C217" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D217" s="14" t="n">
+      <c r="C251" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E217" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F217" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="14" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="13" t="inlineStr">
+      <c r="E251" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" s="59" t="n"/>
+    </row>
+    <row r="252" outlineLevel="1">
+      <c r="A252" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B218" s="13" t="inlineStr">
+      <c r="B252" s="59" t="inlineStr">
         <is>
           <t>Florham Park</t>
         </is>
       </c>
-      <c r="C218" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D218" s="13" t="n">
+      <c r="C252" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F218" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" s="13" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="14" t="inlineStr">
+      <c r="E252" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="59" t="n"/>
+    </row>
+    <row r="253" outlineLevel="1">
+      <c r="A253" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B219" s="14" t="inlineStr">
+      <c r="B253" s="59" t="inlineStr">
         <is>
           <t>Green Brook Township</t>
         </is>
       </c>
-      <c r="C219" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D219" s="14" t="n">
+      <c r="C253" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F219" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" s="14" t="inlineStr">
+      <c r="E253" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="13" t="inlineStr">
+    <row r="254" outlineLevel="1">
+      <c r="A254" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B220" s="13" t="inlineStr">
+      <c r="B254" s="59" t="inlineStr">
         <is>
           <t>Hewitt</t>
         </is>
       </c>
-      <c r="C220" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D220" s="13" t="n">
+      <c r="C254" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F220" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" s="13" t="inlineStr">
+      <c r="E254" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="14" t="inlineStr">
+    <row r="255" outlineLevel="1">
+      <c r="A255" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B221" s="14" t="inlineStr">
+      <c r="B255" s="59" t="inlineStr">
         <is>
           <t>Jersey City</t>
         </is>
       </c>
-      <c r="C221" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D221" s="14" t="n">
+      <c r="C255" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F221" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" s="14" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="13" t="inlineStr">
+      <c r="E255" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G255" s="59" t="n"/>
+    </row>
+    <row r="256" outlineLevel="1">
+      <c r="A256" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B222" s="13" t="inlineStr">
+      <c r="B256" s="59" t="inlineStr">
         <is>
           <t>Maplewood</t>
         </is>
       </c>
-      <c r="C222" s="13" t="n">
+      <c r="C256" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D222" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F222" s="11" t="n">
+      <c r="D256" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="61" t="n">
         <v>0.5</v>
       </c>
-      <c r="G222" s="13" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="14" t="inlineStr">
+      <c r="G256" s="59" t="n"/>
+    </row>
+    <row r="257" outlineLevel="1">
+      <c r="A257" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B223" s="14" t="inlineStr">
+      <c r="B257" s="59" t="inlineStr">
         <is>
           <t>Montclair</t>
         </is>
       </c>
-      <c r="C223" s="14" t="n">
+      <c r="C257" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="D223" s="14" t="n">
+      <c r="D257" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E223" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F223" s="6" t="n">
+      <c r="E257" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="61" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G223" s="14" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="13" t="inlineStr">
+      <c r="G257" s="59" t="n"/>
+    </row>
+    <row r="258" outlineLevel="1">
+      <c r="A258" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B224" s="13" t="inlineStr">
+      <c r="B258" s="59" t="inlineStr">
         <is>
           <t>Morris Plains</t>
         </is>
       </c>
-      <c r="C224" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D224" s="13" t="n">
+      <c r="C258" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F224" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="13" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="14" t="inlineStr">
+      <c r="E258" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" s="59" t="n"/>
+    </row>
+    <row r="259" outlineLevel="1">
+      <c r="A259" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B225" s="14" t="inlineStr">
+      <c r="B259" s="59" t="inlineStr">
         <is>
           <t>Pittstown</t>
         </is>
       </c>
-      <c r="C225" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D225" s="14" t="n">
+      <c r="C259" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F225" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G225" s="14" t="inlineStr">
+      <c r="E259" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G259" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="13" t="inlineStr">
+    <row r="260" outlineLevel="1">
+      <c r="A260" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B226" s="13" t="inlineStr">
+      <c r="B260" s="59" t="inlineStr">
         <is>
           <t>Pompton Lakes</t>
         </is>
       </c>
-      <c r="C226" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D226" s="13" t="n">
+      <c r="C260" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F226" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G226" s="13" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="14" t="inlineStr">
+      <c r="E260" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G260" s="59" t="n"/>
+    </row>
+    <row r="261" outlineLevel="1">
+      <c r="A261" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B227" s="14" t="inlineStr">
+      <c r="B261" s="59" t="inlineStr">
         <is>
           <t>Short Hills</t>
         </is>
       </c>
-      <c r="C227" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D227" s="14" t="n">
+      <c r="C261" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F227" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G227" s="14" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="13" t="inlineStr">
+      <c r="E261" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="59" t="n"/>
+    </row>
+    <row r="262" outlineLevel="1">
+      <c r="A262" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B228" s="13" t="inlineStr">
+      <c r="B262" s="59" t="inlineStr">
         <is>
           <t>Stewartsville</t>
         </is>
       </c>
-      <c r="C228" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D228" s="13" t="n">
+      <c r="C262" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F228" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G228" s="13" t="inlineStr">
+      <c r="E262" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G262" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="14" t="inlineStr">
+    <row r="263" outlineLevel="1">
+      <c r="A263" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B229" s="14" t="inlineStr">
+      <c r="B263" s="59" t="inlineStr">
         <is>
           <t>West Milford</t>
         </is>
       </c>
-      <c r="C229" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D229" s="14" t="n">
+      <c r="C263" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E229" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G229" s="14" t="inlineStr">
+      <c r="E263" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="13" t="inlineStr">
+    <row r="264" outlineLevel="1">
+      <c r="A264" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B230" s="13" t="inlineStr">
+      <c r="B264" s="59" t="inlineStr">
         <is>
           <t>East Orange</t>
         </is>
       </c>
-      <c r="C230" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D230" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E230" s="13" t="n">
+      <c r="C264" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F230" s="11" t="n">
+      <c r="F264" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G230" s="13" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="14" t="inlineStr">
+      <c r="G264" s="59" t="n"/>
+    </row>
+    <row r="265" outlineLevel="1">
+      <c r="A265" s="59" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B231" s="14" t="inlineStr">
+      <c r="B265" s="59" t="inlineStr">
         <is>
           <t>Summit</t>
         </is>
       </c>
-      <c r="C231" s="14" t="n">
+      <c r="C265" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D231" s="14" t="n">
+      <c r="D265" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="E231" s="14" t="n">
+      <c r="E265" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F231" s="6" t="n">
+      <c r="F265" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="G231" s="14" t="inlineStr"/>
+      <c r="G265" s="59" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B266" s="62" t="inlineStr">
+        <is>
+          <t>24 towns</t>
+        </is>
+      </c>
+      <c r="C266" s="63" t="n">
+        <v>44</v>
+      </c>
+      <c r="D266" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="E266" s="63" t="n">
+        <v>32</v>
+      </c>
+      <c r="F266" s="64" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G266" s="62" t="inlineStr">
+        <is>
+          <t>7 out of area</t>
+        </is>
+      </c>
+    </row>
+    <row r="267"/>
+    <row r="268">
+      <c r="A268" s="65" t="inlineStr">
+        <is>
+          <t>12-month total</t>
+        </is>
+      </c>
+      <c r="B268" s="65" t="inlineStr"/>
+      <c r="C268" s="66" t="n">
+        <v>437</v>
+      </c>
+      <c r="D268" s="66" t="n">
+        <v>185</v>
+      </c>
+      <c r="E268" s="66" t="n">
+        <v>251</v>
+      </c>
+      <c r="F268" s="67" t="n">
+        <v>0.5756880733944955</v>
+      </c>
+      <c r="G268" s="65" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G231"/>
@@ -34589,7 +35131,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>

--- a/KTU-consultation-analysis.xlsx
+++ b/KTU-consultation-analysis.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +170,15 @@
       <color rgb="FF1C5566"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C6122"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF9C6122"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -236,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,6 +365,11 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -41419,14 +41433,14 @@
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B141" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A141" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B141" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $12,996 on 2026-01-22, and that quote has since expired (218 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C141" s="53" t="inlineStr">
@@ -41483,9 +41497,9 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="O141" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O141" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $12,996 · Refacing</t>
         </is>
       </c>
       <c r="P141" s="69" t="inlineStr">
@@ -41517,14 +41531,14 @@
       </c>
     </row>
     <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="49" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B142" s="50" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A142" s="75" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B142" s="76" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $8,842 on 2026-01-30, and that quote has since expired (210 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C142" s="50" t="inlineStr">
@@ -41585,9 +41599,9 @@
           <t>+19735665882</t>
         </is>
       </c>
-      <c r="O142" s="50" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O142" s="76" t="inlineStr">
+        <is>
+          <t>Expired quote $8,842 · Countertops</t>
         </is>
       </c>
       <c r="P142" s="69" t="inlineStr">
@@ -41801,14 +41815,14 @@
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B145" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A145" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B145" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $33,540 on 2026-01-23, and that quote has since expired (217 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C145" s="53" t="inlineStr">
@@ -41865,9 +41879,9 @@
           <t>Yard Signs</t>
         </is>
       </c>
-      <c r="O145" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O145" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $33,540 · Painting</t>
         </is>
       </c>
       <c r="P145" s="69" t="inlineStr">
@@ -41995,14 +42009,14 @@
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B147" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A147" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B147" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $49,726 on 2026-04-04, and that quote has since expired (146 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C147" s="53" t="inlineStr">
@@ -42063,9 +42077,9 @@
           <t>+19735665882</t>
         </is>
       </c>
-      <c r="O147" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O147" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $49,726 · New Cabinets</t>
         </is>
       </c>
       <c r="P147" s="69" t="inlineStr">
@@ -42199,14 +42213,14 @@
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B149" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A149" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B149" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $69,317 on 2026-06-10, and that quote has since expired (79 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C149" s="53" t="inlineStr">
@@ -42267,9 +42281,9 @@
           <t>Paid Search</t>
         </is>
       </c>
-      <c r="O149" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O149" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $69,317 · New Cabinets</t>
         </is>
       </c>
       <c r="P149" s="69" t="inlineStr">
@@ -42296,14 +42310,14 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="49" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B150" s="50" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A150" s="75" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B150" s="76" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $24,228 on 2026-04-24, and that quote has since expired (126 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C150" s="50" t="inlineStr">
@@ -42364,9 +42378,9 @@
           <t>Vehicle Signage</t>
         </is>
       </c>
-      <c r="O150" s="50" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O150" s="76" t="inlineStr">
+        <is>
+          <t>Expired quote $24,228 · Painting</t>
         </is>
       </c>
       <c r="P150" s="69" t="inlineStr">
@@ -42741,14 +42755,14 @@
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B155" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A155" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B155" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $34,143 on 2026-05-29, and that quote has since expired (91 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C155" s="53" t="inlineStr">
@@ -42809,9 +42823,9 @@
           <t>kitchentuneup.com</t>
         </is>
       </c>
-      <c r="O155" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O155" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $34,143 · Painting</t>
         </is>
       </c>
       <c r="P155" s="69" t="inlineStr">
@@ -43307,14 +43321,14 @@
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="52" t="inlineStr">
-        <is>
-          <t>5 — ALREADY BACK, DO NOT CALL</t>
-        </is>
-      </c>
-      <c r="B161" s="53" t="inlineStr">
-        <is>
-          <t>Has attended a consult since</t>
+      <c r="A161" s="73" t="inlineStr">
+        <is>
+          <t>1 — CALL NOW (corrected)</t>
+        </is>
+      </c>
+      <c r="B161" s="74" t="inlineStr">
+        <is>
+          <t>Came back and attended a consult, was quoted $53,569 on 2026-07-22, and that quote has since expired (37 days ago). An earlier version of this sheet said do not call — that was right when it was written and is wrong now.</t>
         </is>
       </c>
       <c r="C161" s="53" t="inlineStr">
@@ -43371,9 +43385,9 @@
         </is>
       </c>
       <c r="N161" s="53" t="inlineStr"/>
-      <c r="O161" s="53" t="inlineStr">
-        <is>
-          <t>has attended a consult since</t>
+      <c r="O161" s="74" t="inlineStr">
+        <is>
+          <t>Expired quote $53,569 · New Cabinets</t>
         </is>
       </c>
       <c r="P161" s="69" t="inlineStr">
@@ -43693,7 +43707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -43978,6 +43992,18 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>CORRECTION — eight "already back" rows</t>
+        </is>
+      </c>
+      <c r="B26" s="72" t="inlineStr">
+        <is>
+          <t>Cross-referencing this list against the expired-proposals pull found eight people the recovery list told the team NOT to call, on the grounds that they had already rebooked and attended. They had — and were then quoted, and the quote lapsed. $286,361 of quoted work, from the highest-intent people in the file: they cancelled once, came back anyway, and sat through a consultation. Those eight rows are re-marked CALL NOW (corrected) in sheet 6. The lesson is that "attended a later consult" is not an outcome — the outcome is what happened to the quote.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
